--- a/data/uploads/ahd_screening.xlsx
+++ b/data/uploads/ahd_screening.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Downloads/MaHIS dataset reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CB7607-101F-7E4A-990B-06185D533DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2CCC32-5783-C04F-AFD3-80F7ED3CE02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="736">
   <si>
     <t>name</t>
   </si>
@@ -589,9 +589,6 @@
     <t>ahd_screening</t>
   </si>
   <si>
-    <t>ADVANCE HIV DISEASE QUARTERY REPORT</t>
-  </si>
-  <si>
     <t>period</t>
   </si>
   <si>
@@ -2243,17 +2240,33 @@
   </si>
   <si>
     <t>Zovirax</t>
+  </si>
+  <si>
+    <t>programs</t>
+  </si>
+  <si>
+    <t>Advanced HIV Disease Register – Facility Monthly Report</t>
+  </si>
+  <si>
+    <t>*AHD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2352,35 +2365,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17120,7 +17134,9 @@
     <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" customWidth="1"/>
-    <col min="4" max="23" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.5" customWidth="1"/>
+    <col min="6" max="23" width="10.83203125" customWidth="1"/>
     <col min="24" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17205,8 +17221,12 @@
       <c r="C2" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -17236,8 +17256,12 @@
       <c r="C3" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -17267,8 +17291,12 @@
       <c r="C4" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -17298,8 +17326,12 @@
       <c r="C5" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -17329,8 +17361,12 @@
       <c r="C6" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -17360,8 +17396,12 @@
       <c r="C7" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -17391,8 +17431,12 @@
       <c r="C8" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -17422,8 +17466,12 @@
       <c r="C9" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -17453,8 +17501,12 @@
       <c r="C10" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -17484,8 +17536,12 @@
       <c r="C11" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -17515,8 +17571,12 @@
       <c r="C12" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -17546,8 +17606,12 @@
       <c r="C13" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -17577,8 +17641,12 @@
       <c r="C14" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -17608,8 +17676,12 @@
       <c r="C15" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -17639,8 +17711,12 @@
       <c r="C16" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -17670,8 +17746,12 @@
       <c r="C17" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -17701,8 +17781,12 @@
       <c r="C18" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -17732,8 +17816,12 @@
       <c r="C19" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -17763,8 +17851,12 @@
       <c r="C20" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="D20" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -17794,8 +17886,12 @@
       <c r="C21" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="D21" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -17825,8 +17921,12 @@
       <c r="C22" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -17856,8 +17956,12 @@
       <c r="C23" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="D23" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -17887,8 +17991,12 @@
       <c r="C24" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
+      <c r="D24" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -17918,8 +18026,12 @@
       <c r="C25" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+      <c r="D25" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -17949,8 +18061,12 @@
       <c r="C26" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -17980,8 +18096,12 @@
       <c r="C27" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
+      <c r="D27" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -18011,8 +18131,12 @@
       <c r="C28" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+      <c r="D28" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -18042,8 +18166,12 @@
       <c r="C29" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="D29" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -18073,8 +18201,12 @@
       <c r="C30" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -18104,8 +18236,12 @@
       <c r="C31" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -18135,8 +18271,12 @@
       <c r="C32" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -18166,8 +18306,12 @@
       <c r="C33" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="D33" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -18197,8 +18341,12 @@
       <c r="C34" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
+      <c r="D34" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -18228,8 +18376,12 @@
       <c r="C35" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="D35" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -18259,8 +18411,12 @@
       <c r="C36" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
+      <c r="D36" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -18290,8 +18446,12 @@
       <c r="C37" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
+      <c r="D37" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
@@ -18321,8 +18481,12 @@
       <c r="C38" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="D38" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -18352,8 +18516,12 @@
       <c r="C39" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
+      <c r="D39" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -18383,8 +18551,12 @@
       <c r="C40" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
+      <c r="D40" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -18414,8 +18586,12 @@
       <c r="C41" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
+      <c r="D41" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -18445,8 +18621,12 @@
       <c r="C42" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
+      <c r="D42" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -18476,8 +18656,12 @@
       <c r="C43" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
+      <c r="D43" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -18507,8 +18691,12 @@
       <c r="C44" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
+      <c r="D44" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -18538,8 +18726,12 @@
       <c r="C45" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
+      <c r="D45" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -18569,8 +18761,12 @@
       <c r="C46" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
+      <c r="D46" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -18600,8 +18796,12 @@
       <c r="C47" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
+      <c r="D47" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -18631,8 +18831,12 @@
       <c r="C48" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
+      <c r="D48" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -18662,8 +18866,12 @@
       <c r="C49" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
+      <c r="D49" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -18693,8 +18901,12 @@
       <c r="C50" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+      <c r="D50" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -18724,8 +18936,12 @@
       <c r="C51" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
+      <c r="D51" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -18755,8 +18971,12 @@
       <c r="C52" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
+      <c r="D52" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -18786,8 +19006,12 @@
       <c r="C53" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
+      <c r="D53" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -18817,8 +19041,12 @@
       <c r="C54" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
+      <c r="D54" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -18848,8 +19076,12 @@
       <c r="C55" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
+      <c r="D55" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -18879,8 +19111,12 @@
       <c r="C56" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
+      <c r="D56" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -18910,8 +19146,12 @@
       <c r="C57" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
+      <c r="D57" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -18941,8 +19181,12 @@
       <c r="C58" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
+      <c r="D58" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -18972,8 +19216,12 @@
       <c r="C59" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
+      <c r="D59" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -19003,8 +19251,12 @@
       <c r="C60" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
+      <c r="D60" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -19034,8 +19286,12 @@
       <c r="C61" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
+      <c r="D61" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -19065,8 +19321,12 @@
       <c r="C62" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
+      <c r="D62" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -19096,8 +19356,12 @@
       <c r="C63" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
+      <c r="D63" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -19127,8 +19391,12 @@
       <c r="C64" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
+      <c r="D64" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -19158,8 +19426,12 @@
       <c r="C65" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
+      <c r="D65" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -19189,8 +19461,12 @@
       <c r="C66" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
+      <c r="D66" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -19220,8 +19496,12 @@
       <c r="C67" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
+      <c r="D67" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -19251,8 +19531,12 @@
       <c r="C68" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
+      <c r="D68" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -19282,8 +19566,12 @@
       <c r="C69" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
+      <c r="D69" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -19313,8 +19601,12 @@
       <c r="C70" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
+      <c r="D70" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -19344,8 +19636,12 @@
       <c r="C71" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
+      <c r="D71" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -19375,8 +19671,12 @@
       <c r="C72" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
+      <c r="D72" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>735</v>
+      </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -42279,42 +42579,48 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B1000"/>
+  <dimension ref="A1:C1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>180</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1">
+      <c r="C1" s="18" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="5" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="6" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="7" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="8" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="9" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="10" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="11" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="12" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="13" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="14" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="15" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="16" spans="1:2" ht="15.75" customHeight="1"/>
+      <c r="B2" s="18" t="s">
+        <v>734</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -43315,15 +43621,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1">
       <c r="A2" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>184</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1"/>
@@ -44343,10 +44649,10 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -44361,13 +44667,13 @@
         <v>ahd_screening</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
@@ -50381,77 +50687,77 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
       <c r="A1" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="C1" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="D1" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="E1" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="F1" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="15" t="s">
         <v>198</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
       <c r="A2" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="D2" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="12" t="s">
         <v>203</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>204</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>179</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1">
       <c r="A3" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>207</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>208</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>177</v>
@@ -50460,804 +50766,804 @@
         <v>178</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1">
       <c r="A4" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="C4" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="E4" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="G4" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>214</v>
-      </c>
       <c r="I4" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1">
       <c r="A5" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="C5" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="E5" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="I5" s="12" t="s">
         <v>218</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
       <c r="A6" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="C6" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="I6" s="12" t="s">
         <v>222</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1">
       <c r="A7" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="C7" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="I7" s="12" t="s">
         <v>226</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
       <c r="A8" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="C8" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>230</v>
-      </c>
       <c r="I8" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="B9" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>232</v>
-      </c>
       <c r="I9" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
       <c r="B10" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>234</v>
-      </c>
       <c r="I10" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
       <c r="B11" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="I11" s="12" t="s">
         <v>236</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
       <c r="B12" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>238</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1">
       <c r="B13" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>240</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>242</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1">
       <c r="B15" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>244</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1">
       <c r="B16" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>246</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="15.75" customHeight="1">
       <c r="B17" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>248</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="15.75" customHeight="1">
       <c r="B18" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>250</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="15.75" customHeight="1">
       <c r="B19" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>252</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="15.75" customHeight="1">
       <c r="B20" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>254</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="15.75" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>256</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="15.75" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>258</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="15.75" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>260</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="15.75" customHeight="1">
       <c r="B24" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>262</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="15.75" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>264</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="15.75" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>266</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="15.75" customHeight="1">
       <c r="B27" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>268</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="15.75" customHeight="1">
       <c r="B28" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="15.75" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>272</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="15.75" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="15.75" customHeight="1">
       <c r="B31" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>276</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="15.75" customHeight="1">
       <c r="C32" s="12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="3:3" ht="15.75" customHeight="1">
       <c r="C33" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="3:3" ht="15.75" customHeight="1">
       <c r="C34" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="3:3" ht="15.75" customHeight="1">
       <c r="C35" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="3:3" ht="15.75" customHeight="1">
       <c r="C36" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37" spans="3:3" ht="15.75" customHeight="1">
       <c r="C37" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" spans="3:3" ht="15.75" customHeight="1">
       <c r="C38" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="3:3" ht="15.75" customHeight="1">
       <c r="C39" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="3:3" ht="15.75" customHeight="1">
       <c r="C40" s="12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41" spans="3:3" ht="15.75" customHeight="1">
       <c r="C41" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42" spans="3:3" ht="15.75" customHeight="1">
       <c r="C42" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" spans="3:3" ht="15.75" customHeight="1">
       <c r="C43" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="3:3" ht="15.75" customHeight="1">
       <c r="C44" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="45" spans="3:3" ht="15.75" customHeight="1">
       <c r="C45" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="46" spans="3:3" ht="15.75" customHeight="1">
       <c r="C46" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47" spans="3:3" ht="15.75" customHeight="1">
       <c r="C47" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="48" spans="3:3" ht="15.75" customHeight="1">
       <c r="C48" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="49" spans="3:3" ht="15.75" customHeight="1">
       <c r="C49" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="50" spans="3:3" ht="15.75" customHeight="1">
       <c r="C50" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="51" spans="3:3" ht="15.75" customHeight="1">
       <c r="C51" s="12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="52" spans="3:3" ht="15.75" customHeight="1">
       <c r="C52" s="12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="3:3" ht="15.75" customHeight="1">
       <c r="C53" s="12" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="54" spans="3:3" ht="15.75" customHeight="1">
       <c r="C54" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55" spans="3:3" ht="15.75" customHeight="1">
       <c r="C55" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" spans="3:3" ht="15.75" customHeight="1">
       <c r="C56" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="57" spans="3:3" ht="15.75" customHeight="1">
       <c r="C57" s="12" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="58" spans="3:3" ht="15.75" customHeight="1">
       <c r="C58" s="12" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="59" spans="3:3" ht="15.75" customHeight="1">
       <c r="C59" s="12" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="60" spans="3:3" ht="15.75" customHeight="1">
       <c r="C60" s="12" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="61" spans="3:3" ht="15.75" customHeight="1">
       <c r="C61" s="12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="62" spans="3:3" ht="15.75" customHeight="1">
       <c r="C62" s="12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="63" spans="3:3" ht="15.75" customHeight="1">
       <c r="C63" s="12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="3:3" ht="15.75" customHeight="1">
       <c r="C64" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65" spans="3:3" ht="15.75" customHeight="1">
       <c r="C65" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="66" spans="3:3" ht="15.75" customHeight="1">
       <c r="C66" s="12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="67" spans="3:3" ht="15.75" customHeight="1">
       <c r="C67" s="12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="68" spans="3:3" ht="15.75" customHeight="1">
       <c r="C68" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="69" spans="3:3" ht="15.75" customHeight="1">
       <c r="C69" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="70" spans="3:3" ht="15.75" customHeight="1">
       <c r="C70" s="12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="71" spans="3:3" ht="15.75" customHeight="1">
       <c r="C71" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="72" spans="3:3" ht="15.75" customHeight="1">
       <c r="C72" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="73" spans="3:3" ht="15.75" customHeight="1">
       <c r="C73" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="74" spans="3:3" ht="15.75" customHeight="1">
       <c r="C74" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="75" spans="3:3" ht="15.75" customHeight="1">
       <c r="C75" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="76" spans="3:3" ht="15.75" customHeight="1">
       <c r="C76" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="77" spans="3:3" ht="15.75" customHeight="1">
       <c r="C77" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="78" spans="3:3" ht="15.75" customHeight="1">
       <c r="C78" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="79" spans="3:3" ht="15.75" customHeight="1">
       <c r="C79" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="80" spans="3:3" ht="15.75" customHeight="1">
       <c r="C80" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="81" spans="3:3" ht="15.75" customHeight="1">
       <c r="C81" s="12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="82" spans="3:3" ht="15.75" customHeight="1">
       <c r="C82" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="83" spans="3:3" ht="15.75" customHeight="1">
       <c r="C83" s="12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="84" spans="3:3" ht="15.75" customHeight="1">
       <c r="C84" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="85" spans="3:3" ht="15.75" customHeight="1">
       <c r="C85" s="12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="86" spans="3:3" ht="15.75" customHeight="1">
       <c r="C86" s="12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="87" spans="3:3" ht="15.75" customHeight="1">
       <c r="C87" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="88" spans="3:3" ht="15.75" customHeight="1">
       <c r="C88" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="89" spans="3:3" ht="15.75" customHeight="1">
       <c r="C89" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="90" spans="3:3" ht="15.75" customHeight="1">
       <c r="C90" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="91" spans="3:3" ht="15.75" customHeight="1">
       <c r="C91" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="92" spans="3:3" ht="15.75" customHeight="1">
       <c r="C92" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="93" spans="3:3" ht="15.75" customHeight="1">
       <c r="C93" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="94" spans="3:3" ht="15.75" customHeight="1">
       <c r="C94" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="95" spans="3:3" ht="15.75" customHeight="1">
       <c r="C95" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="96" spans="3:3" ht="15.75" customHeight="1">
       <c r="C96" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="97" spans="3:3" ht="15.75" customHeight="1">
       <c r="C97" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="98" spans="3:3" ht="15.75" customHeight="1">
       <c r="C98" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="99" spans="3:3" ht="15.75" customHeight="1">
       <c r="C99" s="12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="100" spans="3:3" ht="15.75" customHeight="1">
       <c r="C100" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="101" spans="3:3" ht="15.75" customHeight="1">
       <c r="C101" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="102" spans="3:3" ht="15.75" customHeight="1">
       <c r="C102" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="103" spans="3:3" ht="15.75" customHeight="1">
       <c r="C103" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="104" spans="3:3" ht="15.75" customHeight="1">
       <c r="C104" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="105" spans="3:3" ht="15.75" customHeight="1">
       <c r="C105" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="106" spans="3:3" ht="15.75" customHeight="1">
       <c r="C106" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="107" spans="3:3" ht="15.75" customHeight="1">
       <c r="C107" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="108" spans="3:3" ht="15.75" customHeight="1">
       <c r="C108" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="109" spans="3:3" ht="15.75" customHeight="1">
       <c r="C109" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="110" spans="3:3" ht="15.75" customHeight="1">
       <c r="C110" s="12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="111" spans="3:3" ht="15.75" customHeight="1">
       <c r="C111" s="12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="112" spans="3:3" ht="15.75" customHeight="1">
       <c r="C112" s="12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="113" spans="3:3" ht="15.75" customHeight="1">
       <c r="C113" s="12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="114" spans="3:3" ht="15.75" customHeight="1">
       <c r="C114" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="115" spans="3:3" ht="15.75" customHeight="1">
       <c r="C115" s="12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="116" spans="3:3" ht="15.75" customHeight="1">
       <c r="C116" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="117" spans="3:3" ht="15.75" customHeight="1">
       <c r="C117" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="118" spans="3:3" ht="15.75" customHeight="1">
       <c r="C118" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="119" spans="3:3" ht="15.75" customHeight="1">
       <c r="C119" s="12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="120" spans="3:3" ht="15.75" customHeight="1">
       <c r="C120" s="12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="121" spans="3:3" ht="15.75" customHeight="1">
       <c r="C121" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="122" spans="3:3" ht="15.75" customHeight="1">
       <c r="C122" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="123" spans="3:3" ht="15.75" customHeight="1">
       <c r="C123" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="124" spans="3:3" ht="15.75" customHeight="1">
       <c r="C124" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="125" spans="3:3" ht="15.75" customHeight="1">
       <c r="C125" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="126" spans="3:3" ht="15.75" customHeight="1">
       <c r="C126" s="12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="127" spans="3:3" ht="15.75" customHeight="1">
       <c r="C127" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="128" spans="3:3" ht="15.75" customHeight="1">
       <c r="C128" s="12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="129" spans="3:3" ht="15.75" customHeight="1">
       <c r="C129" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="130" spans="3:3" ht="15.75" customHeight="1">
       <c r="C130" s="12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="131" spans="3:3" ht="15.75" customHeight="1">
       <c r="C131" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="132" spans="3:3" ht="15.75" customHeight="1">
       <c r="C132" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="133" spans="3:3" ht="15.75" customHeight="1">
       <c r="C133" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="134" spans="3:3" ht="15.75" customHeight="1">
       <c r="C134" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="135" spans="3:3" ht="15.75" customHeight="1">
       <c r="C135" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="3:3" ht="15.75" customHeight="1">
       <c r="C136" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="137" spans="3:3" ht="15.75" customHeight="1">
@@ -51267,122 +51573,122 @@
     </row>
     <row r="138" spans="3:3" ht="15.75" customHeight="1">
       <c r="C138" s="12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="139" spans="3:3" ht="15.75" customHeight="1">
       <c r="C139" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="140" spans="3:3" ht="15.75" customHeight="1">
       <c r="C140" s="12" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="141" spans="3:3" ht="15.75" customHeight="1">
       <c r="C141" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="142" spans="3:3" ht="15.75" customHeight="1">
       <c r="C142" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="143" spans="3:3" ht="15.75" customHeight="1">
       <c r="C143" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="144" spans="3:3" ht="15.75" customHeight="1">
       <c r="C144" s="12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="145" spans="3:3" ht="15.75" customHeight="1">
       <c r="C145" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="146" spans="3:3" ht="15.75" customHeight="1">
       <c r="C146" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="147" spans="3:3" ht="15.75" customHeight="1">
       <c r="C147" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="148" spans="3:3" ht="15.75" customHeight="1">
       <c r="C148" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="149" spans="3:3" ht="15.75" customHeight="1">
       <c r="C149" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="150" spans="3:3" ht="15.75" customHeight="1">
       <c r="C150" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="151" spans="3:3" ht="15.75" customHeight="1">
       <c r="C151" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="152" spans="3:3" ht="15.75" customHeight="1">
       <c r="C152" s="12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="3:3" ht="15.75" customHeight="1">
       <c r="C153" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="154" spans="3:3" ht="15.75" customHeight="1">
       <c r="C154" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="3:3" ht="15.75" customHeight="1">
       <c r="C155" s="12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="156" spans="3:3" ht="15.75" customHeight="1">
       <c r="C156" s="12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="157" spans="3:3" ht="15.75" customHeight="1">
       <c r="C157" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="158" spans="3:3" ht="15.75" customHeight="1">
       <c r="C158" s="12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="159" spans="3:3" ht="15.75" customHeight="1">
       <c r="C159" s="12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="160" spans="3:3" ht="15.75" customHeight="1">
       <c r="C160" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="161" spans="3:3" ht="15.75" customHeight="1">
       <c r="C161" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="162" spans="3:3" ht="15.75" customHeight="1">
@@ -51392,852 +51698,852 @@
     </row>
     <row r="163" spans="3:3" ht="15.75" customHeight="1">
       <c r="C163" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="164" spans="3:3" ht="15.75" customHeight="1">
       <c r="C164" s="12" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="165" spans="3:3" ht="15.75" customHeight="1">
       <c r="C165" s="12" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="166" spans="3:3" ht="15.75" customHeight="1">
       <c r="C166" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="167" spans="3:3" ht="15.75" customHeight="1">
       <c r="C167" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="168" spans="3:3" ht="15.75" customHeight="1">
       <c r="C168" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="169" spans="3:3" ht="15.75" customHeight="1">
       <c r="C169" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="170" spans="3:3" ht="15.75" customHeight="1">
       <c r="C170" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="171" spans="3:3" ht="15.75" customHeight="1">
       <c r="C171" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="172" spans="3:3" ht="15.75" customHeight="1">
       <c r="C172" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="173" spans="3:3" ht="15.75" customHeight="1">
       <c r="C173" s="12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="174" spans="3:3" ht="15.75" customHeight="1">
       <c r="C174" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="175" spans="3:3" ht="15.75" customHeight="1">
       <c r="C175" s="12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="176" spans="3:3" ht="15.75" customHeight="1">
       <c r="C176" s="12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="177" spans="3:3" ht="15.75" customHeight="1">
       <c r="C177" s="12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="178" spans="3:3" ht="15.75" customHeight="1">
       <c r="C178" s="12" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="179" spans="3:3" ht="15.75" customHeight="1">
       <c r="C179" s="12" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" spans="3:3" ht="15.75" customHeight="1">
       <c r="C180" s="12" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="3:3" ht="15.75" customHeight="1">
       <c r="C181" s="12" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="3:3" ht="15.75" customHeight="1">
       <c r="C182" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="3:3" ht="15.75" customHeight="1">
       <c r="C183" s="12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="3:3" ht="15.75" customHeight="1">
       <c r="C184" s="12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="3:3" ht="15.75" customHeight="1">
       <c r="C185" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="186" spans="3:3" ht="15.75" customHeight="1">
       <c r="C186" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="187" spans="3:3" ht="15.75" customHeight="1">
       <c r="C187" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="188" spans="3:3" ht="15.75" customHeight="1">
       <c r="C188" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="189" spans="3:3" ht="15.75" customHeight="1">
       <c r="C189" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="190" spans="3:3" ht="15.75" customHeight="1">
       <c r="C190" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="191" spans="3:3" ht="15.75" customHeight="1">
       <c r="C191" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="192" spans="3:3" ht="15.75" customHeight="1">
       <c r="C192" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="193" spans="3:3" ht="15.75" customHeight="1">
       <c r="C193" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="194" spans="3:3" ht="15.75" customHeight="1">
       <c r="C194" s="12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="195" spans="3:3" ht="15.75" customHeight="1">
       <c r="C195" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="196" spans="3:3" ht="15.75" customHeight="1">
       <c r="C196" s="12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="197" spans="3:3" ht="15.75" customHeight="1">
       <c r="C197" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="198" spans="3:3" ht="15.75" customHeight="1">
       <c r="C198" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="199" spans="3:3" ht="15.75" customHeight="1">
       <c r="C199" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="200" spans="3:3" ht="15.75" customHeight="1">
       <c r="C200" s="12" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="201" spans="3:3" ht="15.75" customHeight="1">
       <c r="C201" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="202" spans="3:3" ht="15.75" customHeight="1">
       <c r="C202" s="12" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="203" spans="3:3" ht="15.75" customHeight="1">
       <c r="C203" s="12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="204" spans="3:3" ht="15.75" customHeight="1">
       <c r="C204" s="12" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="205" spans="3:3" ht="15.75" customHeight="1">
       <c r="C205" s="12" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="206" spans="3:3" ht="15.75" customHeight="1">
       <c r="C206" s="12" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="207" spans="3:3" ht="15.75" customHeight="1">
       <c r="C207" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="208" spans="3:3" ht="15.75" customHeight="1">
       <c r="C208" s="12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="209" spans="3:3" ht="15.75" customHeight="1">
       <c r="C209" s="12" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="210" spans="3:3" ht="15.75" customHeight="1">
       <c r="C210" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="211" spans="3:3" ht="15.75" customHeight="1">
       <c r="C211" s="12" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="212" spans="3:3" ht="15.75" customHeight="1">
       <c r="C212" s="12" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="213" spans="3:3" ht="15.75" customHeight="1">
       <c r="C213" s="12" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="214" spans="3:3" ht="15.75" customHeight="1">
       <c r="C214" s="12" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="215" spans="3:3" ht="15.75" customHeight="1">
       <c r="C215" s="12" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="216" spans="3:3" ht="15.75" customHeight="1">
       <c r="C216" s="12" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="217" spans="3:3" ht="15.75" customHeight="1">
       <c r="C217" s="12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="218" spans="3:3" ht="15.75" customHeight="1">
       <c r="C218" s="12" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="219" spans="3:3" ht="15.75" customHeight="1">
       <c r="C219" s="12" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="220" spans="3:3" ht="15.75" customHeight="1">
       <c r="C220" s="12" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="221" spans="3:3" ht="15.75" customHeight="1">
       <c r="C221" s="12" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="222" spans="3:3" ht="15.75" customHeight="1">
       <c r="C222" s="12" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="223" spans="3:3" ht="15.75" customHeight="1">
       <c r="C223" s="12" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="224" spans="3:3" ht="15.75" customHeight="1">
       <c r="C224" s="12" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="225" spans="3:3" ht="15.75" customHeight="1">
       <c r="C225" s="12" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="226" spans="3:3" ht="15.75" customHeight="1">
       <c r="C226" s="12" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="227" spans="3:3" ht="15.75" customHeight="1">
       <c r="C227" s="12" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="228" spans="3:3" ht="15.75" customHeight="1">
       <c r="C228" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="229" spans="3:3" ht="15.75" customHeight="1">
       <c r="C229" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="230" spans="3:3" ht="15.75" customHeight="1">
       <c r="C230" s="12" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="231" spans="3:3" ht="15.75" customHeight="1">
       <c r="C231" s="12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="232" spans="3:3" ht="15.75" customHeight="1">
       <c r="C232" s="12" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="233" spans="3:3" ht="15.75" customHeight="1">
       <c r="C233" s="12" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="234" spans="3:3" ht="15.75" customHeight="1">
       <c r="C234" s="12" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="235" spans="3:3" ht="15.75" customHeight="1">
       <c r="C235" s="12" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="236" spans="3:3" ht="15.75" customHeight="1">
       <c r="C236" s="12" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="237" spans="3:3" ht="15.75" customHeight="1">
       <c r="C237" s="12" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="238" spans="3:3" ht="15.75" customHeight="1">
       <c r="C238" s="12" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="239" spans="3:3" ht="15.75" customHeight="1">
       <c r="C239" s="12" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="240" spans="3:3" ht="15.75" customHeight="1">
       <c r="C240" s="12" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="241" spans="3:3" ht="15.75" customHeight="1">
       <c r="C241" s="12" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="242" spans="3:3" ht="15.75" customHeight="1">
       <c r="C242" s="12" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="243" spans="3:3" ht="15.75" customHeight="1">
       <c r="C243" s="12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="244" spans="3:3" ht="15.75" customHeight="1">
       <c r="C244" s="12" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="245" spans="3:3" ht="15.75" customHeight="1">
       <c r="C245" s="12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="246" spans="3:3" ht="15.75" customHeight="1">
       <c r="C246" s="12" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="247" spans="3:3" ht="15.75" customHeight="1">
       <c r="C247" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="248" spans="3:3" ht="15.75" customHeight="1">
       <c r="C248" s="12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="249" spans="3:3" ht="15.75" customHeight="1">
       <c r="C249" s="12" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="250" spans="3:3" ht="15.75" customHeight="1">
       <c r="C250" s="12" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="251" spans="3:3" ht="15.75" customHeight="1">
       <c r="C251" s="12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="252" spans="3:3" ht="15.75" customHeight="1">
       <c r="C252" s="12" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="253" spans="3:3" ht="15.75" customHeight="1">
       <c r="C253" s="12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="254" spans="3:3" ht="15.75" customHeight="1">
       <c r="C254" s="12" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="255" spans="3:3" ht="15.75" customHeight="1">
       <c r="C255" s="12" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="256" spans="3:3" ht="15.75" customHeight="1">
       <c r="C256" s="12" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="257" spans="3:3" ht="15.75" customHeight="1">
       <c r="C257" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="258" spans="3:3" ht="15.75" customHeight="1">
       <c r="C258" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="259" spans="3:3" ht="15.75" customHeight="1">
       <c r="C259" s="12" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="260" spans="3:3" ht="15.75" customHeight="1">
       <c r="C260" s="12" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="261" spans="3:3" ht="15.75" customHeight="1">
       <c r="C261" s="12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="262" spans="3:3" ht="15.75" customHeight="1">
       <c r="C262" s="12" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="263" spans="3:3" ht="15.75" customHeight="1">
       <c r="C263" s="12" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="264" spans="3:3" ht="15.75" customHeight="1">
       <c r="C264" s="12" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="265" spans="3:3" ht="15.75" customHeight="1">
       <c r="C265" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="266" spans="3:3" ht="15.75" customHeight="1">
       <c r="C266" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="267" spans="3:3" ht="15.75" customHeight="1">
       <c r="C267" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="268" spans="3:3" ht="15.75" customHeight="1">
       <c r="C268" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="269" spans="3:3" ht="15.75" customHeight="1">
       <c r="C269" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="270" spans="3:3" ht="15.75" customHeight="1">
       <c r="C270" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="271" spans="3:3" ht="15.75" customHeight="1">
       <c r="C271" s="12" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="272" spans="3:3" ht="15.75" customHeight="1">
       <c r="C272" s="12" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="273" spans="3:3" ht="15.75" customHeight="1">
       <c r="C273" s="12" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="274" spans="3:3" ht="15.75" customHeight="1">
       <c r="C274" s="12" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="275" spans="3:3" ht="15.75" customHeight="1">
       <c r="C275" s="12" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="276" spans="3:3" ht="15.75" customHeight="1">
       <c r="C276" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="277" spans="3:3" ht="15.75" customHeight="1">
       <c r="C277" s="12" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="278" spans="3:3" ht="15.75" customHeight="1">
       <c r="C278" s="12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="279" spans="3:3" ht="15.75" customHeight="1">
       <c r="C279" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="280" spans="3:3" ht="15.75" customHeight="1">
       <c r="C280" s="12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="281" spans="3:3" ht="15.75" customHeight="1">
       <c r="C281" s="12" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="282" spans="3:3" ht="15.75" customHeight="1">
       <c r="C282" s="12" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="283" spans="3:3" ht="15.75" customHeight="1">
       <c r="C283" s="12" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="284" spans="3:3" ht="15.75" customHeight="1">
       <c r="C284" s="12" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="285" spans="3:3" ht="15.75" customHeight="1">
       <c r="C285" s="12" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="286" spans="3:3" ht="15.75" customHeight="1">
       <c r="C286" s="12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="287" spans="3:3" ht="15.75" customHeight="1">
       <c r="C287" s="12" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="288" spans="3:3" ht="15.75" customHeight="1">
       <c r="C288" s="12" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="289" spans="3:3" ht="15.75" customHeight="1">
       <c r="C289" s="12" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="290" spans="3:3" ht="15.75" customHeight="1">
       <c r="C290" s="12" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="291" spans="3:3" ht="15.75" customHeight="1">
       <c r="C291" s="12" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="292" spans="3:3" ht="15.75" customHeight="1">
       <c r="C292" s="12" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="293" spans="3:3" ht="15.75" customHeight="1">
       <c r="C293" s="12" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="294" spans="3:3" ht="15.75" customHeight="1">
       <c r="C294" s="12" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="295" spans="3:3" ht="15.75" customHeight="1">
       <c r="C295" s="12" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="296" spans="3:3" ht="15.75" customHeight="1">
       <c r="C296" s="12" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="297" spans="3:3" ht="15.75" customHeight="1">
       <c r="C297" s="12" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="298" spans="3:3" ht="15.75" customHeight="1">
       <c r="C298" s="12" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="299" spans="3:3" ht="15.75" customHeight="1">
       <c r="C299" s="12" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="300" spans="3:3" ht="15.75" customHeight="1">
       <c r="C300" s="12" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="301" spans="3:3" ht="15.75" customHeight="1">
       <c r="C301" s="12" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="302" spans="3:3" ht="15.75" customHeight="1">
       <c r="C302" s="12" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="303" spans="3:3" ht="15.75" customHeight="1">
       <c r="C303" s="12" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="304" spans="3:3" ht="15.75" customHeight="1">
       <c r="C304" s="12" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="305" spans="3:3" ht="15.75" customHeight="1">
       <c r="C305" s="12" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="306" spans="3:3" ht="15.75" customHeight="1">
       <c r="C306" s="12" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="307" spans="3:3" ht="15.75" customHeight="1">
       <c r="C307" s="12" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="308" spans="3:3" ht="15.75" customHeight="1">
       <c r="C308" s="12" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="309" spans="3:3" ht="15.75" customHeight="1">
       <c r="C309" s="12" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="310" spans="3:3" ht="15.75" customHeight="1">
       <c r="C310" s="12" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="311" spans="3:3" ht="15.75" customHeight="1">
       <c r="C311" s="12" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="312" spans="3:3" ht="15.75" customHeight="1">
       <c r="C312" s="12" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="313" spans="3:3" ht="15.75" customHeight="1">
       <c r="C313" s="12" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="314" spans="3:3" ht="15.75" customHeight="1">
       <c r="C314" s="12" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="315" spans="3:3" ht="15.75" customHeight="1">
       <c r="C315" s="12" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="316" spans="3:3" ht="15.75" customHeight="1">
       <c r="C316" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="317" spans="3:3" ht="15.75" customHeight="1">
       <c r="C317" s="12" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="318" spans="3:3" ht="15.75" customHeight="1">
       <c r="C318" s="12" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="319" spans="3:3" ht="15.75" customHeight="1">
       <c r="C319" s="12" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="320" spans="3:3" ht="15.75" customHeight="1">
       <c r="C320" s="12" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="321" spans="3:3" ht="15.75" customHeight="1">
       <c r="C321" s="12" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="322" spans="3:3" ht="15.75" customHeight="1">
       <c r="C322" s="12" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="323" spans="3:3" ht="15.75" customHeight="1">
       <c r="C323" s="12" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="324" spans="3:3" ht="15.75" customHeight="1">
       <c r="C324" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="325" spans="3:3" ht="15.75" customHeight="1">
       <c r="C325" s="12" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="326" spans="3:3" ht="15.75" customHeight="1">
       <c r="C326" s="12" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="327" spans="3:3" ht="15.75" customHeight="1">
       <c r="C327" s="12" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="328" spans="3:3" ht="15.75" customHeight="1">
       <c r="C328" s="12" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="329" spans="3:3" ht="15.75" customHeight="1">
       <c r="C329" s="12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="330" spans="3:3" ht="15.75" customHeight="1">
       <c r="C330" s="12" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="331" spans="3:3" ht="15.75" customHeight="1">
       <c r="C331" s="12" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="332" spans="3:3" ht="15.75" customHeight="1">
       <c r="C332" s="12" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="333" spans="3:3" ht="15.75" customHeight="1">
@@ -52247,97 +52553,97 @@
     </row>
     <row r="334" spans="3:3" ht="15.75" customHeight="1">
       <c r="C334" s="12" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="335" spans="3:3" ht="15.75" customHeight="1">
       <c r="C335" s="12" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="336" spans="3:3" ht="15.75" customHeight="1">
       <c r="C336" s="12" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="337" spans="3:3" ht="15.75" customHeight="1">
       <c r="C337" s="12" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="338" spans="3:3" ht="15.75" customHeight="1">
       <c r="C338" s="12" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="339" spans="3:3" ht="15.75" customHeight="1">
       <c r="C339" s="12" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="340" spans="3:3" ht="15.75" customHeight="1">
       <c r="C340" s="12" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="341" spans="3:3" ht="15.75" customHeight="1">
       <c r="C341" s="12" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="342" spans="3:3" ht="15.75" customHeight="1">
       <c r="C342" s="12" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="343" spans="3:3" ht="15.75" customHeight="1">
       <c r="C343" s="12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="344" spans="3:3" ht="15.75" customHeight="1">
       <c r="C344" s="12" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="345" spans="3:3" ht="15.75" customHeight="1">
       <c r="C345" s="12" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="346" spans="3:3" ht="15.75" customHeight="1">
       <c r="C346" s="12" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="347" spans="3:3" ht="15.75" customHeight="1">
       <c r="C347" s="12" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="348" spans="3:3" ht="15.75" customHeight="1">
       <c r="C348" s="12" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="349" spans="3:3" ht="15.75" customHeight="1">
       <c r="C349" s="12" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="350" spans="3:3" ht="15.75" customHeight="1">
       <c r="C350" s="12" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="351" spans="3:3" ht="15.75" customHeight="1">
       <c r="C351" s="12" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="352" spans="3:3" ht="15.75" customHeight="1">
       <c r="C352" s="12" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="353" spans="3:3" ht="15.75" customHeight="1">
@@ -52347,292 +52653,292 @@
     </row>
     <row r="354" spans="3:3" ht="15.75" customHeight="1">
       <c r="C354" s="12" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="355" spans="3:3" ht="15.75" customHeight="1">
       <c r="C355" s="12" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="356" spans="3:3" ht="15.75" customHeight="1">
       <c r="C356" s="12" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="357" spans="3:3" ht="15.75" customHeight="1">
       <c r="C357" s="12" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="358" spans="3:3" ht="15.75" customHeight="1">
       <c r="C358" s="12" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="359" spans="3:3" ht="15.75" customHeight="1">
       <c r="C359" s="12" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="360" spans="3:3" ht="15.75" customHeight="1">
       <c r="C360" s="12" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="361" spans="3:3" ht="15.75" customHeight="1">
       <c r="C361" s="12" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="362" spans="3:3" ht="15.75" customHeight="1">
       <c r="C362" s="12" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="363" spans="3:3" ht="15.75" customHeight="1">
       <c r="C363" s="12" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="364" spans="3:3" ht="15.75" customHeight="1">
       <c r="C364" s="12" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="365" spans="3:3" ht="15.75" customHeight="1">
       <c r="C365" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="366" spans="3:3" ht="15.75" customHeight="1">
       <c r="C366" s="12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="367" spans="3:3" ht="15.75" customHeight="1">
       <c r="C367" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="368" spans="3:3" ht="15.75" customHeight="1">
       <c r="C368" s="12" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="369" spans="3:3" ht="15.75" customHeight="1">
       <c r="C369" s="12" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="370" spans="3:3" ht="15.75" customHeight="1">
       <c r="C370" s="12" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="371" spans="3:3" ht="15.75" customHeight="1">
       <c r="C371" s="12" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="372" spans="3:3" ht="15.75" customHeight="1">
       <c r="C372" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="373" spans="3:3" ht="15.75" customHeight="1">
       <c r="C373" s="12" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="374" spans="3:3" ht="15.75" customHeight="1">
       <c r="C374" s="12" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="375" spans="3:3" ht="15.75" customHeight="1">
       <c r="C375" s="12" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="376" spans="3:3" ht="15.75" customHeight="1">
       <c r="C376" s="12" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="377" spans="3:3" ht="15.75" customHeight="1">
       <c r="C377" s="12" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="378" spans="3:3" ht="15.75" customHeight="1">
       <c r="C378" s="12" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="379" spans="3:3" ht="15.75" customHeight="1">
       <c r="C379" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="380" spans="3:3" ht="15.75" customHeight="1">
       <c r="C380" s="12" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="381" spans="3:3" ht="15.75" customHeight="1">
       <c r="C381" s="12" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="382" spans="3:3" ht="15.75" customHeight="1">
       <c r="C382" s="12" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="383" spans="3:3" ht="15.75" customHeight="1">
       <c r="C383" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="384" spans="3:3" ht="15.75" customHeight="1">
       <c r="C384" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="385" spans="3:3" ht="15.75" customHeight="1">
       <c r="C385" s="12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="386" spans="3:3" ht="15.75" customHeight="1">
       <c r="C386" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="387" spans="3:3" ht="15.75" customHeight="1">
       <c r="C387" s="12" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="388" spans="3:3" ht="15.75" customHeight="1">
       <c r="C388" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="389" spans="3:3" ht="15.75" customHeight="1">
       <c r="C389" s="12" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="390" spans="3:3" ht="15.75" customHeight="1">
       <c r="C390" s="12" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="391" spans="3:3" ht="15.75" customHeight="1">
       <c r="C391" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="392" spans="3:3" ht="15.75" customHeight="1">
       <c r="C392" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="393" spans="3:3" ht="15.75" customHeight="1">
       <c r="C393" s="12" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="394" spans="3:3" ht="15.75" customHeight="1">
       <c r="C394" s="12" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="395" spans="3:3" ht="15.75" customHeight="1">
       <c r="C395" s="12" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="396" spans="3:3" ht="15.75" customHeight="1">
       <c r="C396" s="12" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="397" spans="3:3" ht="15.75" customHeight="1">
       <c r="C397" s="12" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="398" spans="3:3" ht="15.75" customHeight="1">
       <c r="C398" s="12" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="399" spans="3:3" ht="15.75" customHeight="1">
       <c r="C399" s="12" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="400" spans="3:3" ht="15.75" customHeight="1">
       <c r="C400" s="12" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="401" spans="3:3" ht="15.75" customHeight="1">
       <c r="C401" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="402" spans="3:3" ht="15.75" customHeight="1">
       <c r="C402" s="12" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="403" spans="3:3" ht="15.75" customHeight="1">
       <c r="C403" s="12" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="404" spans="3:3" ht="15.75" customHeight="1">
       <c r="C404" s="12" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="405" spans="3:3" ht="15.75" customHeight="1">
       <c r="C405" s="12" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="406" spans="3:3" ht="15.75" customHeight="1">
       <c r="C406" s="12" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="407" spans="3:3" ht="15.75" customHeight="1">
       <c r="C407" s="12" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="408" spans="3:3" ht="15.75" customHeight="1">
       <c r="C408" s="12" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="409" spans="3:3" ht="15.75" customHeight="1">
       <c r="C409" s="12" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="410" spans="3:3" ht="15.75" customHeight="1">
       <c r="C410" s="12" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="411" spans="3:3" ht="15.75" customHeight="1">
       <c r="C411" s="12" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="412" spans="3:3" ht="15.75" customHeight="1">
@@ -52642,402 +52948,402 @@
     </row>
     <row r="413" spans="3:3" ht="15.75" customHeight="1">
       <c r="C413" s="12" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="414" spans="3:3" ht="15.75" customHeight="1">
       <c r="C414" s="12" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="415" spans="3:3" ht="15.75" customHeight="1">
       <c r="C415" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="416" spans="3:3" ht="15.75" customHeight="1">
       <c r="C416" s="12" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="417" spans="3:3" ht="15.75" customHeight="1">
       <c r="C417" s="12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="418" spans="3:3" ht="15.75" customHeight="1">
       <c r="C418" s="12" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="419" spans="3:3" ht="15.75" customHeight="1">
       <c r="C419" s="12" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="420" spans="3:3" ht="15.75" customHeight="1">
       <c r="C420" s="12" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="421" spans="3:3" ht="15.75" customHeight="1">
       <c r="C421" s="12" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="422" spans="3:3" ht="15.75" customHeight="1">
       <c r="C422" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="423" spans="3:3" ht="15.75" customHeight="1">
       <c r="C423" s="12" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="424" spans="3:3" ht="15.75" customHeight="1">
       <c r="C424" s="12" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="425" spans="3:3" ht="15.75" customHeight="1">
       <c r="C425" s="12" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="426" spans="3:3" ht="15.75" customHeight="1">
       <c r="C426" s="12" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="427" spans="3:3" ht="15.75" customHeight="1">
       <c r="C427" s="12" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="428" spans="3:3" ht="15.75" customHeight="1">
       <c r="C428" s="12" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="429" spans="3:3" ht="15.75" customHeight="1">
       <c r="C429" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="430" spans="3:3" ht="15.75" customHeight="1">
       <c r="C430" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="431" spans="3:3" ht="15.75" customHeight="1">
       <c r="C431" s="12" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="432" spans="3:3" ht="15.75" customHeight="1">
       <c r="C432" s="12" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="433" spans="3:3" ht="15.75" customHeight="1">
       <c r="C433" s="12" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="434" spans="3:3" ht="15.75" customHeight="1">
       <c r="C434" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="435" spans="3:3" ht="15.75" customHeight="1">
       <c r="C435" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="436" spans="3:3" ht="15.75" customHeight="1">
       <c r="C436" s="12" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="437" spans="3:3" ht="15.75" customHeight="1">
       <c r="C437" s="12" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="438" spans="3:3" ht="15.75" customHeight="1">
       <c r="C438" s="12" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="439" spans="3:3" ht="15.75" customHeight="1">
       <c r="C439" s="12" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="440" spans="3:3" ht="15.75" customHeight="1">
       <c r="C440" s="12" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="441" spans="3:3" ht="15.75" customHeight="1">
       <c r="C441" s="12" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="442" spans="3:3" ht="15.75" customHeight="1">
       <c r="C442" s="12" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="443" spans="3:3" ht="15.75" customHeight="1">
       <c r="C443" s="12" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="444" spans="3:3" ht="15.75" customHeight="1">
       <c r="C444" s="12" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="445" spans="3:3" ht="15.75" customHeight="1">
       <c r="C445" s="12" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="446" spans="3:3" ht="15.75" customHeight="1">
       <c r="C446" s="12" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="447" spans="3:3" ht="15.75" customHeight="1">
       <c r="C447" s="12" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="448" spans="3:3" ht="15.75" customHeight="1">
       <c r="C448" s="12" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="449" spans="3:3" ht="15.75" customHeight="1">
       <c r="C449" s="12" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="450" spans="3:3" ht="15.75" customHeight="1">
       <c r="C450" s="12" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="451" spans="3:3" ht="15.75" customHeight="1">
       <c r="C451" s="12" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="452" spans="3:3" ht="15.75" customHeight="1">
       <c r="C452" s="12" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="453" spans="3:3" ht="15.75" customHeight="1">
       <c r="C453" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="454" spans="3:3" ht="15.75" customHeight="1">
       <c r="C454" s="12" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="455" spans="3:3" ht="15.75" customHeight="1">
       <c r="C455" s="12" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="456" spans="3:3" ht="15.75" customHeight="1">
       <c r="C456" s="12" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="457" spans="3:3" ht="15.75" customHeight="1">
       <c r="C457" s="12" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="458" spans="3:3" ht="15.75" customHeight="1">
       <c r="C458" s="12" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="459" spans="3:3" ht="15.75" customHeight="1">
       <c r="C459" s="12" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="460" spans="3:3" ht="15.75" customHeight="1">
       <c r="C460" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="461" spans="3:3" ht="15.75" customHeight="1">
       <c r="C461" s="12" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="462" spans="3:3" ht="15.75" customHeight="1">
       <c r="C462" s="12" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="463" spans="3:3" ht="15.75" customHeight="1">
       <c r="C463" s="12" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="464" spans="3:3" ht="15.75" customHeight="1">
       <c r="C464" s="12" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="465" spans="3:3" ht="15.75" customHeight="1">
       <c r="C465" s="12" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="466" spans="3:3" ht="15.75" customHeight="1">
       <c r="C466" s="12" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="467" spans="3:3" ht="15.75" customHeight="1">
       <c r="C467" s="12" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="468" spans="3:3" ht="15.75" customHeight="1">
       <c r="C468" s="12" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="469" spans="3:3" ht="15.75" customHeight="1">
       <c r="C469" s="12" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="470" spans="3:3" ht="15.75" customHeight="1">
       <c r="C470" s="12" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="471" spans="3:3" ht="15.75" customHeight="1">
       <c r="C471" s="12" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="472" spans="3:3" ht="15.75" customHeight="1">
       <c r="C472" s="12" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="473" spans="3:3" ht="15.75" customHeight="1">
       <c r="C473" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="474" spans="3:3" ht="15.75" customHeight="1">
       <c r="C474" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="475" spans="3:3" ht="15.75" customHeight="1">
       <c r="C475" s="12" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="476" spans="3:3" ht="15.75" customHeight="1">
       <c r="C476" s="12" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="477" spans="3:3" ht="15.75" customHeight="1">
       <c r="C477" s="12" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="478" spans="3:3" ht="15.75" customHeight="1">
       <c r="C478" s="12" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="479" spans="3:3" ht="15.75" customHeight="1">
       <c r="C479" s="12" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="480" spans="3:3" ht="15.75" customHeight="1">
       <c r="C480" s="12" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="481" spans="3:3" ht="15.75" customHeight="1">
       <c r="C481" s="12" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="482" spans="3:3" ht="15.75" customHeight="1">
       <c r="C482" s="12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="483" spans="3:3" ht="15.75" customHeight="1">
       <c r="C483" s="12" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="484" spans="3:3" ht="15.75" customHeight="1">
       <c r="C484" s="12" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="485" spans="3:3" ht="15.75" customHeight="1">
       <c r="C485" s="12" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="486" spans="3:3" ht="15.75" customHeight="1">
       <c r="C486" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="487" spans="3:3" ht="15.75" customHeight="1">
       <c r="C487" s="12" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="488" spans="3:3" ht="15.75" customHeight="1">
       <c r="C488" s="12" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="489" spans="3:3" ht="15.75" customHeight="1">
       <c r="C489" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="490" spans="3:3" ht="15.75" customHeight="1">
       <c r="C490" s="12" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="491" spans="3:3" ht="15.75" customHeight="1">
       <c r="C491" s="12" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="492" spans="3:3" ht="15.75" customHeight="1">
       <c r="C492" s="12" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="493" spans="3:3" ht="15.75" customHeight="1"/>

--- a/data/uploads/ahd_screening.xlsx
+++ b/data/uploads/ahd_screening.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Downloads/MaHIS dataset reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/innocentwowa/Documents/Python Scripts/DashPlotly/data/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2CCC32-5783-C04F-AFD3-80F7ED3CE02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFBDC88-FE2C-6C45-8D62-7AFD2A37D52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18020" yWindow="760" windowWidth="16540" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VARIABLE_NAMES" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="737">
   <si>
     <t>name</t>
   </si>
@@ -2249,6 +2249,9 @@
   </si>
   <si>
     <t>*AHD</t>
+  </si>
+  <si>
+    <t>Ahd screening</t>
   </si>
 </sst>
 </file>
@@ -17225,10 +17228,14 @@
         <v>191</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>735</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+        <v>736</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -17250,8 +17257,8 @@
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>179</v>
+      <c r="B3" s="12" t="s">
+        <v>177</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>178</v>
@@ -17260,12 +17267,16 @@
         <v>191</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -17295,12 +17306,16 @@
         <v>191</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -17330,12 +17345,16 @@
         <v>191</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -17365,7 +17384,7 @@
         <v>191</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>

--- a/data/uploads/ahd_screening.xlsx
+++ b/data/uploads/ahd_screening.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="840">
   <si>
     <t>name</t>
   </si>
@@ -173,6 +173,9 @@
     <t>Kx1ztD4x9XO</t>
   </si>
   <si>
+    <t>last_taken_arvs_total_screened</t>
+  </si>
+  <si>
     <t>Seriously Ill</t>
   </si>
   <si>
@@ -191,6 +194,9 @@
     <t>IxtSV2ceN59</t>
   </si>
   <si>
+    <t>seriously_ill_total_screened</t>
+  </si>
+  <si>
     <t>AHD Symptoms Screening</t>
   </si>
   <si>
@@ -269,6 +275,9 @@
     <t>Total Symptoms</t>
   </si>
   <si>
+    <t>ahd_symptoms_screening_total_symptoms</t>
+  </si>
+  <si>
     <t>WHO Clinical Stage</t>
   </si>
   <si>
@@ -638,6 +647,9 @@
     <t>sex_total_screened</t>
   </si>
   <si>
+    <t>nunique</t>
+  </si>
+  <si>
     <t>age_0-4</t>
   </si>
   <si>
@@ -698,60 +710,99 @@
     <t>last_taken_arvs_current</t>
   </si>
   <si>
-    <t>last_taken_arvs_total_screened</t>
-  </si>
-  <si>
     <t>seriously_ill_no</t>
   </si>
   <si>
+    <t>Patient outcome</t>
+  </si>
+  <si>
+    <t>!=Admitted | !=Death</t>
+  </si>
+  <si>
     <t>seriously_ill_yes</t>
   </si>
   <si>
+    <t>Admitted</t>
+  </si>
+  <si>
     <t>seriously_ill_unknown_missing</t>
   </si>
   <si>
-    <t>seriously_ill_total_screened</t>
+    <t>_</t>
   </si>
   <si>
     <t>ahd_symptoms_screening_cough</t>
   </si>
   <si>
+    <t>Presenting complaints</t>
+  </si>
+  <si>
+    <t>*cough</t>
+  </si>
+  <si>
     <t>ahd_symptoms_screening_weight_loss_no_thrive</t>
   </si>
   <si>
+    <t>*weight loss</t>
+  </si>
+  <si>
     <t>ahd_symptoms_screening_fever_night_sweats</t>
   </si>
   <si>
+    <t>*night sweat</t>
+  </si>
+  <si>
     <t>ahd_symptoms_screening_mouth_sores</t>
   </si>
   <si>
+    <t>*mouth sore</t>
+  </si>
+  <si>
     <t>ahd_symptoms_screening_shortness_of_breath</t>
   </si>
   <si>
+    <t>*shortness of breath</t>
+  </si>
+  <si>
     <t>ahd_symptoms_screening_cns</t>
   </si>
   <si>
+    <t>*cns</t>
+  </si>
+  <si>
     <t>ahd_symptoms_screening_yellow_eyes</t>
   </si>
   <si>
+    <t>*yellow eyes</t>
+  </si>
+  <si>
     <t>ahd_symptoms_screening_vomiting_abdo_pain</t>
   </si>
   <si>
+    <t>*vomiting | *abdominal pain</t>
+  </si>
+  <si>
     <t>ahd_symptoms_screening_diarrhoea</t>
   </si>
   <si>
+    <t>*diarrhea | *diarrhoea</t>
+  </si>
+  <si>
     <t>ahd_symptoms_screening_peripheral_neuropathy</t>
   </si>
   <si>
+    <t>*peripheral neuropathy</t>
+  </si>
+  <si>
     <t>ahd_symptoms_screening_rash_arms_legs_trunk</t>
   </si>
   <si>
+    <t>*rash</t>
+  </si>
+  <si>
     <t>ahd_symptoms_screening_unknown_missing</t>
   </si>
   <si>
-    <t>ahd_symptoms_screening_total_symptoms</t>
-  </si>
-  <si>
     <t>who_clinical_stage_who_1</t>
   </si>
   <si>
@@ -1146,9 +1197,6 @@
   </si>
   <si>
     <t>Acyclovir</t>
-  </si>
-  <si>
-    <t>Admitted</t>
   </si>
   <si>
     <t>Agrees to followup</t>
@@ -2599,7 +2647,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2649,6 +2697,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
@@ -3320,7 +3371,9 @@
         <v>23</v>
       </c>
       <c r="B23" s="1"/>
-      <c r="C23" s="2"/>
+      <c r="C23" s="15" t="s">
+        <v>50</v>
+      </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
@@ -3332,7 +3385,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>13</v>
@@ -3351,11 +3404,11 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
@@ -3368,11 +3421,11 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
@@ -3389,7 +3442,7 @@
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
@@ -3405,7 +3458,9 @@
         <v>23</v>
       </c>
       <c r="B28" s="1"/>
-      <c r="C28" s="2"/>
+      <c r="C28" s="15" t="s">
+        <v>57</v>
+      </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -3417,7 +3472,7 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>13</v>
@@ -3436,11 +3491,11 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -3453,11 +3508,11 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -3470,11 +3525,11 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -3487,11 +3542,11 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -3504,11 +3559,11 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -3521,11 +3576,11 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -3538,11 +3593,11 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
@@ -3555,11 +3610,11 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
@@ -3572,11 +3627,11 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
@@ -3589,11 +3644,11 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
@@ -3606,11 +3661,11 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
@@ -3623,11 +3678,11 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
@@ -3640,10 +3695,12 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
+      <c r="C42" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="G42" s="10"/>
@@ -3655,7 +3712,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>13</v>
@@ -3674,11 +3731,11 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
@@ -3691,11 +3748,11 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
@@ -3708,11 +3765,11 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
@@ -3725,11 +3782,11 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
@@ -3746,7 +3803,7 @@
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
@@ -3774,7 +3831,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="16" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>13</v>
@@ -3793,11 +3850,11 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
@@ -3810,11 +3867,11 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
@@ -3827,11 +3884,11 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
@@ -3848,7 +3905,7 @@
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -3876,7 +3933,7 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>13</v>
@@ -3895,11 +3952,11 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E57" s="10"/>
       <c r="F57" s="10"/>
@@ -3912,11 +3969,11 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E58" s="10"/>
       <c r="F58" s="10"/>
@@ -3929,11 +3986,11 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E59" s="10"/>
       <c r="F59" s="10"/>
@@ -3950,7 +4007,7 @@
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E60" s="10"/>
       <c r="F60" s="10"/>
@@ -3978,7 +4035,7 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="16" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>13</v>
@@ -3997,11 +4054,11 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E63" s="10"/>
       <c r="F63" s="10"/>
@@ -4014,11 +4071,11 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E64" s="10"/>
       <c r="F64" s="10"/>
@@ -4031,11 +4088,11 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E65" s="10"/>
       <c r="F65" s="10"/>
@@ -4063,7 +4120,7 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="16" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>13</v>
@@ -4082,11 +4139,11 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E68" s="10"/>
       <c r="F68" s="10"/>
@@ -4099,11 +4156,11 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E69" s="10"/>
       <c r="F69" s="10"/>
@@ -4116,11 +4173,11 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E70" s="10"/>
       <c r="F70" s="10"/>
@@ -4148,7 +4205,7 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="16" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>13</v>
@@ -4167,11 +4224,11 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
@@ -4184,11 +4241,11 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E74" s="10"/>
       <c r="F74" s="10"/>
@@ -4201,11 +4258,11 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E75" s="10"/>
       <c r="F75" s="10"/>
@@ -4233,7 +4290,7 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>13</v>
@@ -4252,11 +4309,11 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
@@ -4269,11 +4326,11 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
@@ -4286,11 +4343,11 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
@@ -4318,7 +4375,7 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>13</v>
@@ -4337,11 +4394,11 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="18" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
@@ -4354,11 +4411,11 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
@@ -4371,11 +4428,11 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="18" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
@@ -4403,7 +4460,7 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="16" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>13</v>
@@ -4422,11 +4479,11 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="19" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
@@ -4439,11 +4496,11 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="19" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
@@ -4456,11 +4513,11 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
@@ -4488,7 +4545,7 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>13</v>
@@ -4507,11 +4564,11 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
@@ -4524,11 +4581,11 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
@@ -4545,7 +4602,7 @@
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
@@ -4573,7 +4630,7 @@
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="16" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>13</v>
@@ -4592,11 +4649,11 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
@@ -4609,11 +4666,11 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="19" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
@@ -4626,11 +4683,11 @@
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
@@ -4643,11 +4700,11 @@
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="19" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
@@ -4660,11 +4717,11 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="19" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -4677,11 +4734,11 @@
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="19" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
@@ -4694,7 +4751,7 @@
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="20"/>
@@ -4709,7 +4766,7 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="16" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>13</v>
@@ -4728,11 +4785,11 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="19" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -4745,11 +4802,11 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="19" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -4762,11 +4819,11 @@
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="19" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
@@ -4779,11 +4836,11 @@
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="19" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
@@ -4800,7 +4857,7 @@
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="19" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
@@ -4813,7 +4870,7 @@
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="20"/>
@@ -17286,76 +17343,76 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
@@ -17363,22 +17420,22 @@
         <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -17405,31 +17462,31 @@
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>192</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -17451,31 +17508,31 @@
         <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="I4" s="22" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -17497,37 +17554,37 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F5" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>192</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -17547,19 +17604,19 @@
         <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
@@ -17585,25 +17642,25 @@
         <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>189</v>
+        <v>209</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>208</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G7" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -17627,31 +17684,31 @@
         <v>29</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>189</v>
+        <v>211</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>208</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G8" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>25</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -17673,25 +17730,25 @@
         <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>189</v>
+        <v>214</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>208</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G9" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -17717,17 +17774,17 @@
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>189</v>
+      <c r="C10" s="9" t="s">
+        <v>208</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
@@ -17753,31 +17810,31 @@
         <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C11" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F11" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>192</v>
-      </c>
       <c r="G11" s="18" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -17799,31 +17856,31 @@
         <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>213</v>
-      </c>
       <c r="H12" s="18" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -17845,31 +17902,31 @@
         <v>39</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="H13" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>214</v>
-      </c>
       <c r="I13" s="18" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -17893,23 +17950,23 @@
       <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>189</v>
+      <c r="C14" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I14" s="18"/>
       <c r="J14" s="18"/>
@@ -17933,19 +17990,19 @@
         <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>189</v>
+        <v>224</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -17971,19 +18028,19 @@
         <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>189</v>
+        <v>226</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -18009,19 +18066,19 @@
         <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>189</v>
+        <v>227</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -18047,19 +18104,19 @@
         <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>189</v>
+        <v>228</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -18081,21 +18138,23 @@
       <c r="X18" s="1"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="2"/>
+      <c r="A19" s="15" t="s">
+        <v>50</v>
+      </c>
       <c r="B19" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>189</v>
+        <v>50</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>221</v>
+        <v>194</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>195</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -18118,27 +18177,35 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>189</v>
+        <v>229</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>231</v>
+      </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -18156,27 +18223,35 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>189</v>
+        <v>232</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>233</v>
+      </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -18194,27 +18269,35 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>189</v>
+        <v>234</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>235</v>
+      </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -18231,24 +18314,26 @@
       <c r="X22" s="1"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2"/>
+      <c r="A23" s="15" t="s">
+        <v>57</v>
+      </c>
       <c r="B23" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>189</v>
+        <v>57</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -18268,27 +18353,35 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>189</v>
+        <v>236</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I24" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J24" s="18" t="s">
+        <v>238</v>
+      </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -18306,27 +18399,35 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>189</v>
+        <v>239</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>240</v>
+      </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -18344,27 +18445,35 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>189</v>
+        <v>241</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I26" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>242</v>
+      </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -18382,27 +18491,35 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>244</v>
+      </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -18420,27 +18537,35 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>189</v>
+        <v>245</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>246</v>
+      </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -18458,27 +18583,35 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>189</v>
+        <v>247</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G29" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I29" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J29" s="18" t="s">
+        <v>248</v>
+      </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -18496,27 +18629,35 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>189</v>
+        <v>249</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G30" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H30" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>250</v>
+      </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -18534,27 +18675,35 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H31" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
+      <c r="I31" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>252</v>
+      </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -18572,27 +18721,35 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>189</v>
+        <v>253</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H32" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J32" s="18" t="s">
+        <v>254</v>
+      </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -18610,27 +18767,35 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>189</v>
+        <v>255</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>256</v>
+      </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -18648,27 +18813,35 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>189</v>
+        <v>257</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G34" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H34" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>258</v>
+      </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -18686,27 +18859,35 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>189</v>
+        <v>259</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G35" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H35" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I35" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J35" s="18" t="s">
+        <v>235</v>
+      </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -18723,25 +18904,31 @@
       <c r="X35" s="1"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="2"/>
+      <c r="A36" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="B36" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>189</v>
+        <v>84</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G36" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H36" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I36" s="18"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -18760,24 +18947,23 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>189</v>
+        <v>260</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G37" s="1"/>
+        <v>225</v>
+      </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -18798,22 +18984,22 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>189</v>
+        <v>261</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -18836,22 +19022,22 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>189</v>
+        <v>262</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -18874,22 +19060,22 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>189</v>
+        <v>263</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -18912,22 +19098,22 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>189</v>
+        <v>264</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -18951,19 +19137,19 @@
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>189</v>
+        <v>265</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -18986,22 +19172,22 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>189</v>
+        <v>266</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -19024,22 +19210,22 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>189</v>
+        <v>267</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -19062,22 +19248,22 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>189</v>
+        <v>268</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -19100,22 +19286,22 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>189</v>
+        <v>269</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -19139,19 +19325,19 @@
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>189</v>
+        <v>270</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -19174,22 +19360,22 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>189</v>
+        <v>271</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -19212,22 +19398,22 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>189</v>
+        <v>272</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -19250,22 +19436,22 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>189</v>
+        <v>273</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -19288,22 +19474,22 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>189</v>
+        <v>274</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -19327,19 +19513,19 @@
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>189</v>
+        <v>275</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -19362,22 +19548,22 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>189</v>
+        <v>276</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -19400,22 +19586,22 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>189</v>
+        <v>277</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -19438,22 +19624,22 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>189</v>
+        <v>278</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -19477,19 +19663,19 @@
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>189</v>
+        <v>279</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -19512,22 +19698,22 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>189</v>
+        <v>280</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -19550,22 +19736,22 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>189</v>
+        <v>281</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -19588,22 +19774,22 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>189</v>
+        <v>282</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -19627,19 +19813,19 @@
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>189</v>
+        <v>283</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -19662,22 +19848,22 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>189</v>
+        <v>284</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -19700,22 +19886,22 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>189</v>
+        <v>285</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -19738,22 +19924,22 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>189</v>
+        <v>286</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -19777,19 +19963,19 @@
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>189</v>
+        <v>287</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -19812,22 +19998,22 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>189</v>
+        <v>284</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -19850,22 +20036,22 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>189</v>
+        <v>285</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -19888,22 +20074,22 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>189</v>
+        <v>286</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -19927,19 +20113,19 @@
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>189</v>
+        <v>287</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D68" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -19962,20 +20148,20 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B69" s="2"/>
-      <c r="C69" s="1" t="s">
-        <v>189</v>
+      <c r="C69" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -19998,20 +20184,20 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B70" s="2"/>
-      <c r="C70" s="1" t="s">
-        <v>189</v>
+      <c r="C70" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -20034,20 +20220,20 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B71" s="2"/>
-      <c r="C71" s="1" t="s">
-        <v>189</v>
+      <c r="C71" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -20071,17 +20257,17 @@
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
-      <c r="C72" s="1" t="s">
-        <v>189</v>
+      <c r="C72" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D72" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -20104,22 +20290,22 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>189</v>
+        <v>288</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -20142,22 +20328,22 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>189</v>
+        <v>289</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D74" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -20180,22 +20366,22 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>189</v>
+        <v>290</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
@@ -20219,19 +20405,19 @@
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="2"/>
       <c r="B76" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>189</v>
+        <v>291</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D76" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
@@ -20254,20 +20440,20 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="19" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B77" s="1"/>
-      <c r="C77" s="1" t="s">
-        <v>189</v>
+      <c r="C77" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
@@ -20290,20 +20476,20 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="19" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B78" s="1"/>
-      <c r="C78" s="1" t="s">
-        <v>189</v>
+      <c r="C78" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D78" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -20326,20 +20512,20 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B79" s="1"/>
-      <c r="C79" s="1" t="s">
-        <v>189</v>
+      <c r="C79" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -20363,17 +20549,17 @@
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="20"/>
       <c r="B80" s="1"/>
-      <c r="C80" s="1" t="s">
-        <v>189</v>
+      <c r="C80" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D80" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -20396,20 +20582,20 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B81" s="1"/>
-      <c r="C81" s="1" t="s">
-        <v>189</v>
+      <c r="C81" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -20432,20 +20618,20 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B82" s="1"/>
-      <c r="C82" s="1" t="s">
-        <v>189</v>
+      <c r="C82" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D82" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
@@ -20468,20 +20654,20 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B83" s="1"/>
-      <c r="C83" s="1" t="s">
-        <v>189</v>
+      <c r="C83" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
@@ -20505,17 +20691,17 @@
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="20"/>
       <c r="B84" s="1"/>
-      <c r="C84" s="1" t="s">
-        <v>189</v>
+      <c r="C84" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D84" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
@@ -20538,20 +20724,20 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B85" s="1"/>
-      <c r="C85" s="1" t="s">
-        <v>189</v>
+      <c r="C85" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D85" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
@@ -20574,20 +20760,20 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="19" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B86" s="1"/>
-      <c r="C86" s="1" t="s">
-        <v>189</v>
+      <c r="C86" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D86" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
@@ -20610,20 +20796,20 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B87" s="1"/>
-      <c r="C87" s="1" t="s">
-        <v>189</v>
+      <c r="C87" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D87" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
@@ -20646,20 +20832,20 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="19" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B88" s="1"/>
-      <c r="C88" s="1" t="s">
-        <v>189</v>
+      <c r="C88" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D88" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
@@ -20682,20 +20868,20 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="19" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B89" s="1"/>
-      <c r="C89" s="1" t="s">
-        <v>189</v>
+      <c r="C89" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D89" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
@@ -20718,20 +20904,20 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="19" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B90" s="1"/>
-      <c r="C90" s="1" t="s">
-        <v>189</v>
+      <c r="C90" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D90" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
@@ -20755,17 +20941,17 @@
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
-      <c r="C91" s="1" t="s">
-        <v>189</v>
+      <c r="C91" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D91" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
@@ -20788,20 +20974,20 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="19" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B92" s="1"/>
-      <c r="C92" s="1" t="s">
-        <v>189</v>
+      <c r="C92" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D92" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
@@ -20824,20 +21010,20 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="19" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B93" s="1"/>
-      <c r="C93" s="1" t="s">
-        <v>189</v>
+      <c r="C93" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D93" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
@@ -20860,20 +21046,20 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="19" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B94" s="1"/>
-      <c r="C94" s="1" t="s">
-        <v>189</v>
+      <c r="C94" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D94" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
@@ -20896,20 +21082,20 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="19" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B95" s="1"/>
-      <c r="C95" s="1" t="s">
-        <v>189</v>
+      <c r="C95" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D95" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
@@ -20932,20 +21118,20 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="19" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B96" s="1"/>
-      <c r="C96" s="1" t="s">
-        <v>189</v>
+      <c r="C96" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D96" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
@@ -20969,17 +21155,17 @@
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="20"/>
       <c r="B97" s="1"/>
-      <c r="C97" s="1" t="s">
-        <v>189</v>
+      <c r="C97" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="D97" s="18" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
@@ -44264,24 +44450,24 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1"/>
@@ -45302,15 +45488,15 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1"/>
@@ -46334,10 +46520,10 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -46352,13 +46538,13 @@
         <v>ahd_screening</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -52375,2664 +52561,2664 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>293</v>
+      <c r="A1" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>196</v>
+        <v>312</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>199</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E3" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="E3" s="27" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>305</v>
+        <v>321</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>322</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>310</v>
+        <v>326</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>327</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="B9" s="2" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="B10" s="2" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="B11" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="B12" s="2" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="B13" s="2" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="B14" s="2" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="B15" s="2" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="B16" s="2" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="B17" s="2" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="B18" s="2" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="B19" s="2" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="B20" s="2" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="2" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="2" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="2" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="2" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="B25" s="2" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="B26" s="2" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="2" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="2" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="2" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="2" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="C32" s="2" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="C33" s="2" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="C34" s="2" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="C35" s="2" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="C36" s="2" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="C37" s="2" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="C38" s="2" t="s">
-        <v>375</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="C39" s="2" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="C40" s="2" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="C41" s="2" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="C42" s="2" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="C43" s="2" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="C44" s="2" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="C45" s="2" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="C46" s="2" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="C47" s="2" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="C48" s="2" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="C49" s="2" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="C50" s="2" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="C51" s="2" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="C52" s="2" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="C53" s="2" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="C54" s="2" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="C55" s="2" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="C56" s="2" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="C57" s="2" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="C58" s="2" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="C59" s="2" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="C60" s="2" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="C61" s="2" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="C62" s="2" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="C63" s="2" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="C64" s="2" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="C65" s="2" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="C66" s="2" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="C67" s="2" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="C68" s="2" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="C69" s="2" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="C70" s="2" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="C71" s="2" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="C72" s="2" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="C73" s="2" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="C74" s="2" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="C75" s="2" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="C76" s="2" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="C77" s="2" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="C78" s="2" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="C79" s="2" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="C80" s="2" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="C81" s="2" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="C82" s="2" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="C83" s="2" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="C84" s="2" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="C85" s="2" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="C86" s="2" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="C87" s="2" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="C88" s="2" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="C89" s="2" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="C90" s="2" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="C91" s="2" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="C92" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="C93" s="2" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="C94" s="2" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="C95" s="2" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="C96" s="2" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="C97" s="2" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="C98" s="2" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="C99" s="2" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="C100" s="2" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="C101" s="2" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="C102" s="2" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="C103" s="2" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="C104" s="2" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="C105" s="2" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="C106" s="2" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="C107" s="2" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="C108" s="2" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="C109" s="2" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="C110" s="2" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="C111" s="2" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="C112" s="2" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="C113" s="2" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="C114" s="2" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="C115" s="2" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="C116" s="2" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="C117" s="2" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="C118" s="2" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="C119" s="2" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="C120" s="2" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="C121" s="2" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="C122" s="2" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="C123" s="2" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="C124" s="2" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="C125" s="2" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="C126" s="2" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="C127" s="2" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="C128" s="2" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="C129" s="2" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="C130" s="2" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="C131" s="2" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="C132" s="2" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="C133" s="2" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="C134" s="2" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="C135" s="2" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="C136" s="2" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="C137" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="C138" s="2" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="C139" s="2" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="C140" s="2" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="C141" s="2" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="C142" s="2" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="C143" s="2" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="C144" s="2" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="C145" s="2" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="C146" s="2" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="C147" s="2" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="C148" s="2" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="C149" s="2" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="C150" s="2" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="C151" s="2" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="C152" s="2" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="C153" s="2" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="C154" s="2" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="C155" s="2" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="C156" s="2" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="C157" s="2" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="C158" s="2" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="C159" s="2" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="C160" s="2" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="C161" s="2" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="C162" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="C163" s="2" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="C164" s="2" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="C165" s="2" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="C166" s="2" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="C167" s="2" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="C168" s="2" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="C169" s="2" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="C170" s="2" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="C171" s="2" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="C172" s="2" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="C173" s="2" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="C174" s="2" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="C175" s="2" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="C176" s="2" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="C177" s="2" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="C178" s="2" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="C179" s="2" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="C180" s="2" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="C181" s="2" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="C182" s="2" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="C183" s="2" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="C184" s="2" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="C185" s="2" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="C186" s="2" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="C187" s="2" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="C188" s="2" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="C189" s="2" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="C190" s="2" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="C191" s="2" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="C192" s="2" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="C193" s="2" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="C194" s="2" t="s">
-        <v>529</v>
+        <v>545</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="C195" s="2" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="C196" s="2" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="C197" s="2" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="C198" s="2" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="C199" s="2" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="C200" s="2" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="C201" s="2" t="s">
-        <v>536</v>
+        <v>552</v>
       </c>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="C202" s="2" t="s">
-        <v>537</v>
+        <v>553</v>
       </c>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="C203" s="2" t="s">
-        <v>538</v>
+        <v>554</v>
       </c>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="C204" s="2" t="s">
-        <v>539</v>
+        <v>555</v>
       </c>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="C205" s="2" t="s">
-        <v>540</v>
+        <v>556</v>
       </c>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="C206" s="2" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="C207" s="2" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="C208" s="2" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="C209" s="2" t="s">
-        <v>544</v>
+        <v>560</v>
       </c>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="C210" s="2" t="s">
-        <v>545</v>
+        <v>561</v>
       </c>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="C211" s="2" t="s">
-        <v>546</v>
+        <v>562</v>
       </c>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="C212" s="2" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="C213" s="2" t="s">
-        <v>548</v>
+        <v>564</v>
       </c>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="C214" s="2" t="s">
-        <v>549</v>
+        <v>565</v>
       </c>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="C215" s="2" t="s">
-        <v>550</v>
+        <v>566</v>
       </c>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="C216" s="2" t="s">
-        <v>551</v>
+        <v>567</v>
       </c>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="C217" s="2" t="s">
-        <v>552</v>
+        <v>568</v>
       </c>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="C218" s="2" t="s">
-        <v>553</v>
+        <v>569</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="C219" s="2" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="C220" s="2" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="C221" s="2" t="s">
-        <v>556</v>
+        <v>572</v>
       </c>
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="C222" s="2" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="C223" s="2" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="C224" s="2" t="s">
-        <v>559</v>
+        <v>575</v>
       </c>
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="C225" s="2" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="C226" s="2" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="C227" s="2" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="C228" s="2" t="s">
-        <v>563</v>
+        <v>579</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="C229" s="2" t="s">
-        <v>564</v>
+        <v>580</v>
       </c>
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="C230" s="2" t="s">
-        <v>565</v>
+        <v>581</v>
       </c>
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="C231" s="2" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="C232" s="2" t="s">
-        <v>567</v>
+        <v>583</v>
       </c>
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="C233" s="2" t="s">
-        <v>568</v>
+        <v>584</v>
       </c>
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="C234" s="2" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="C235" s="2" t="s">
-        <v>570</v>
+        <v>586</v>
       </c>
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="C236" s="2" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="C237" s="2" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="C238" s="2" t="s">
-        <v>573</v>
+        <v>589</v>
       </c>
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="C239" s="2" t="s">
-        <v>574</v>
+        <v>590</v>
       </c>
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="C240" s="2" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="C241" s="2" t="s">
-        <v>576</v>
+        <v>592</v>
       </c>
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="C242" s="2" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
     </row>
     <row r="243" ht="15.75" customHeight="1">
       <c r="C243" s="2" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
     </row>
     <row r="244" ht="15.75" customHeight="1">
       <c r="C244" s="2" t="s">
-        <v>579</v>
+        <v>595</v>
       </c>
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="C245" s="2" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="C246" s="2" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="C247" s="2" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="C248" s="2" t="s">
-        <v>583</v>
+        <v>599</v>
       </c>
     </row>
     <row r="249" ht="15.75" customHeight="1">
       <c r="C249" s="2" t="s">
-        <v>584</v>
+        <v>600</v>
       </c>
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="C250" s="2" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="C251" s="2" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
     </row>
     <row r="252" ht="15.75" customHeight="1">
       <c r="C252" s="2" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="C253" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="C254" s="2" t="s">
-        <v>588</v>
+        <v>604</v>
       </c>
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="C255" s="2" t="s">
-        <v>589</v>
+        <v>605</v>
       </c>
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="C256" s="2" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="C257" s="2" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="C258" s="2" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="C259" s="2" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="C260" s="2" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="C261" s="2" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="C262" s="2" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="C263" s="2" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="C264" s="2" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="C265" s="2" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="C266" s="2" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="C267" s="2" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="C268" s="2" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="C269" s="2" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="C270" s="2" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="C271" s="2" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="C272" s="2" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="C273" s="2" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="C274" s="2" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="C275" s="2" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="C276" s="2" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="C277" s="2" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="C278" s="2" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="C279" s="2" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="C280" s="2" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="C281" s="2" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
     </row>
     <row r="282" ht="15.75" customHeight="1">
       <c r="C282" s="2" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="C283" s="2" t="s">
-        <v>617</v>
+        <v>633</v>
       </c>
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="C284" s="2" t="s">
-        <v>618</v>
+        <v>634</v>
       </c>
     </row>
     <row r="285" ht="15.75" customHeight="1">
       <c r="C285" s="2" t="s">
-        <v>619</v>
+        <v>635</v>
       </c>
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="C286" s="2" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
     </row>
     <row r="287" ht="15.75" customHeight="1">
       <c r="C287" s="2" t="s">
-        <v>621</v>
+        <v>637</v>
       </c>
     </row>
     <row r="288" ht="15.75" customHeight="1">
       <c r="C288" s="2" t="s">
-        <v>622</v>
+        <v>638</v>
       </c>
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="C289" s="2" t="s">
-        <v>623</v>
+        <v>639</v>
       </c>
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="C290" s="2" t="s">
-        <v>624</v>
+        <v>640</v>
       </c>
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="C291" s="2" t="s">
-        <v>625</v>
+        <v>641</v>
       </c>
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="C292" s="2" t="s">
-        <v>626</v>
+        <v>642</v>
       </c>
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="C293" s="2" t="s">
-        <v>627</v>
+        <v>643</v>
       </c>
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="C294" s="2" t="s">
-        <v>628</v>
+        <v>644</v>
       </c>
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="C295" s="2" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="C296" s="2" t="s">
-        <v>630</v>
+        <v>646</v>
       </c>
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="C297" s="2" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="C298" s="2" t="s">
-        <v>632</v>
+        <v>648</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="C299" s="2" t="s">
-        <v>633</v>
+        <v>649</v>
       </c>
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="C300" s="2" t="s">
-        <v>634</v>
+        <v>650</v>
       </c>
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="C301" s="2" t="s">
-        <v>635</v>
+        <v>651</v>
       </c>
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="C302" s="2" t="s">
-        <v>636</v>
+        <v>652</v>
       </c>
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="C303" s="2" t="s">
-        <v>637</v>
+        <v>653</v>
       </c>
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="C304" s="2" t="s">
-        <v>638</v>
+        <v>654</v>
       </c>
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="C305" s="2" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="C306" s="2" t="s">
-        <v>640</v>
+        <v>656</v>
       </c>
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="C307" s="2" t="s">
-        <v>641</v>
+        <v>657</v>
       </c>
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="C308" s="2" t="s">
-        <v>642</v>
+        <v>658</v>
       </c>
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="C309" s="2" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="C310" s="2" t="s">
-        <v>644</v>
+        <v>660</v>
       </c>
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="C311" s="2" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="C312" s="2" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="C313" s="2" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="C314" s="2" t="s">
-        <v>648</v>
+        <v>664</v>
       </c>
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="C315" s="2" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="C316" s="2" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="C317" s="2" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="C318" s="2" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="C319" s="2" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="C320" s="2" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="C321" s="2" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="C322" s="2" t="s">
-        <v>656</v>
+        <v>672</v>
       </c>
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="C323" s="2" t="s">
-        <v>657</v>
+        <v>673</v>
       </c>
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="C324" s="2" t="s">
-        <v>658</v>
+        <v>674</v>
       </c>
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="C325" s="2" t="s">
-        <v>659</v>
+        <v>675</v>
       </c>
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="C326" s="2" t="s">
-        <v>660</v>
+        <v>676</v>
       </c>
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="C327" s="2" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="C328" s="2" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="C329" s="2" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
     </row>
     <row r="330" ht="15.75" customHeight="1">
       <c r="C330" s="2" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="C331" s="2" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="C332" s="2" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="C333" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="C334" s="2" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="C335" s="2" t="s">
-        <v>668</v>
+        <v>684</v>
       </c>
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="C336" s="2" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="C337" s="2" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="C338" s="2" t="s">
-        <v>671</v>
+        <v>687</v>
       </c>
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="C339" s="2" t="s">
-        <v>672</v>
+        <v>688</v>
       </c>
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="C340" s="2" t="s">
-        <v>673</v>
+        <v>689</v>
       </c>
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="C341" s="2" t="s">
-        <v>674</v>
+        <v>690</v>
       </c>
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="C342" s="2" t="s">
-        <v>675</v>
+        <v>691</v>
       </c>
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="C343" s="2" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="C344" s="2" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="C345" s="2" t="s">
-        <v>678</v>
+        <v>694</v>
       </c>
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="C346" s="2" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
     </row>
     <row r="347" ht="15.75" customHeight="1">
       <c r="C347" s="2" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
     </row>
     <row r="348" ht="15.75" customHeight="1">
       <c r="C348" s="2" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
     </row>
     <row r="349" ht="15.75" customHeight="1">
       <c r="C349" s="2" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
     </row>
     <row r="350" ht="15.75" customHeight="1">
       <c r="C350" s="2" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
     </row>
     <row r="351" ht="15.75" customHeight="1">
       <c r="C351" s="2" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
     </row>
     <row r="352" ht="15.75" customHeight="1">
       <c r="C352" s="2" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
     </row>
     <row r="353" ht="15.75" customHeight="1">
       <c r="C353" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="354" ht="15.75" customHeight="1">
       <c r="C354" s="2" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
     </row>
     <row r="355" ht="15.75" customHeight="1">
       <c r="C355" s="2" t="s">
-        <v>687</v>
+        <v>703</v>
       </c>
     </row>
     <row r="356" ht="15.75" customHeight="1">
       <c r="C356" s="2" t="s">
-        <v>688</v>
+        <v>704</v>
       </c>
     </row>
     <row r="357" ht="15.75" customHeight="1">
       <c r="C357" s="2" t="s">
-        <v>689</v>
+        <v>705</v>
       </c>
     </row>
     <row r="358" ht="15.75" customHeight="1">
       <c r="C358" s="2" t="s">
-        <v>690</v>
+        <v>706</v>
       </c>
     </row>
     <row r="359" ht="15.75" customHeight="1">
       <c r="C359" s="2" t="s">
-        <v>691</v>
+        <v>707</v>
       </c>
     </row>
     <row r="360" ht="15.75" customHeight="1">
       <c r="C360" s="2" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
     </row>
     <row r="361" ht="15.75" customHeight="1">
       <c r="C361" s="2" t="s">
-        <v>693</v>
+        <v>709</v>
       </c>
     </row>
     <row r="362" ht="15.75" customHeight="1">
       <c r="C362" s="2" t="s">
-        <v>694</v>
+        <v>710</v>
       </c>
     </row>
     <row r="363" ht="15.75" customHeight="1">
       <c r="C363" s="2" t="s">
-        <v>695</v>
+        <v>711</v>
       </c>
     </row>
     <row r="364" ht="15.75" customHeight="1">
       <c r="C364" s="2" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
     </row>
     <row r="365" ht="15.75" customHeight="1">
       <c r="C365" s="2" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
     </row>
     <row r="366" ht="15.75" customHeight="1">
       <c r="C366" s="2" t="s">
-        <v>698</v>
+        <v>714</v>
       </c>
     </row>
     <row r="367" ht="15.75" customHeight="1">
       <c r="C367" s="2" t="s">
-        <v>699</v>
+        <v>715</v>
       </c>
     </row>
     <row r="368" ht="15.75" customHeight="1">
       <c r="C368" s="2" t="s">
-        <v>700</v>
+        <v>716</v>
       </c>
     </row>
     <row r="369" ht="15.75" customHeight="1">
       <c r="C369" s="2" t="s">
-        <v>701</v>
+        <v>717</v>
       </c>
     </row>
     <row r="370" ht="15.75" customHeight="1">
       <c r="C370" s="2" t="s">
-        <v>702</v>
+        <v>718</v>
       </c>
     </row>
     <row r="371" ht="15.75" customHeight="1">
       <c r="C371" s="2" t="s">
-        <v>703</v>
+        <v>719</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1">
       <c r="C372" s="2" t="s">
-        <v>704</v>
+        <v>720</v>
       </c>
     </row>
     <row r="373" ht="15.75" customHeight="1">
       <c r="C373" s="2" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
     </row>
     <row r="374" ht="15.75" customHeight="1">
       <c r="C374" s="2" t="s">
-        <v>706</v>
+        <v>722</v>
       </c>
     </row>
     <row r="375" ht="15.75" customHeight="1">
       <c r="C375" s="2" t="s">
-        <v>707</v>
+        <v>723</v>
       </c>
     </row>
     <row r="376" ht="15.75" customHeight="1">
       <c r="C376" s="2" t="s">
-        <v>708</v>
+        <v>724</v>
       </c>
     </row>
     <row r="377" ht="15.75" customHeight="1">
       <c r="C377" s="2" t="s">
-        <v>709</v>
+        <v>725</v>
       </c>
     </row>
     <row r="378" ht="15.75" customHeight="1">
       <c r="C378" s="2" t="s">
-        <v>710</v>
+        <v>726</v>
       </c>
     </row>
     <row r="379" ht="15.75" customHeight="1">
       <c r="C379" s="2" t="s">
-        <v>711</v>
+        <v>727</v>
       </c>
     </row>
     <row r="380" ht="15.75" customHeight="1">
       <c r="C380" s="2" t="s">
-        <v>712</v>
+        <v>728</v>
       </c>
     </row>
     <row r="381" ht="15.75" customHeight="1">
       <c r="C381" s="2" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
     </row>
     <row r="382" ht="15.75" customHeight="1">
       <c r="C382" s="2" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
     </row>
     <row r="383" ht="15.75" customHeight="1">
       <c r="C383" s="2" t="s">
-        <v>715</v>
+        <v>731</v>
       </c>
     </row>
     <row r="384" ht="15.75" customHeight="1">
       <c r="C384" s="2" t="s">
-        <v>716</v>
+        <v>732</v>
       </c>
     </row>
     <row r="385" ht="15.75" customHeight="1">
       <c r="C385" s="2" t="s">
-        <v>717</v>
+        <v>733</v>
       </c>
     </row>
     <row r="386" ht="15.75" customHeight="1">
       <c r="C386" s="2" t="s">
-        <v>718</v>
+        <v>734</v>
       </c>
     </row>
     <row r="387" ht="15.75" customHeight="1">
       <c r="C387" s="2" t="s">
-        <v>719</v>
+        <v>735</v>
       </c>
     </row>
     <row r="388" ht="15.75" customHeight="1">
       <c r="C388" s="2" t="s">
-        <v>720</v>
+        <v>736</v>
       </c>
     </row>
     <row r="389" ht="15.75" customHeight="1">
       <c r="C389" s="2" t="s">
-        <v>721</v>
+        <v>737</v>
       </c>
     </row>
     <row r="390" ht="15.75" customHeight="1">
       <c r="C390" s="2" t="s">
-        <v>722</v>
+        <v>738</v>
       </c>
     </row>
     <row r="391" ht="15.75" customHeight="1">
       <c r="C391" s="2" t="s">
-        <v>723</v>
+        <v>739</v>
       </c>
     </row>
     <row r="392" ht="15.75" customHeight="1">
       <c r="C392" s="2" t="s">
-        <v>724</v>
+        <v>740</v>
       </c>
     </row>
     <row r="393" ht="15.75" customHeight="1">
       <c r="C393" s="2" t="s">
-        <v>725</v>
+        <v>741</v>
       </c>
     </row>
     <row r="394" ht="15.75" customHeight="1">
       <c r="C394" s="2" t="s">
-        <v>726</v>
+        <v>742</v>
       </c>
     </row>
     <row r="395" ht="15.75" customHeight="1">
       <c r="C395" s="2" t="s">
-        <v>727</v>
+        <v>743</v>
       </c>
     </row>
     <row r="396" ht="15.75" customHeight="1">
       <c r="C396" s="2" t="s">
-        <v>728</v>
+        <v>744</v>
       </c>
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="C397" s="2" t="s">
-        <v>729</v>
+        <v>745</v>
       </c>
     </row>
     <row r="398" ht="15.75" customHeight="1">
       <c r="C398" s="2" t="s">
-        <v>730</v>
+        <v>746</v>
       </c>
     </row>
     <row r="399" ht="15.75" customHeight="1">
       <c r="C399" s="2" t="s">
-        <v>731</v>
+        <v>747</v>
       </c>
     </row>
     <row r="400" ht="15.75" customHeight="1">
       <c r="C400" s="2" t="s">
-        <v>732</v>
+        <v>748</v>
       </c>
     </row>
     <row r="401" ht="15.75" customHeight="1">
       <c r="C401" s="2" t="s">
-        <v>733</v>
+        <v>749</v>
       </c>
     </row>
     <row r="402" ht="15.75" customHeight="1">
       <c r="C402" s="2" t="s">
-        <v>734</v>
+        <v>750</v>
       </c>
     </row>
     <row r="403" ht="15.75" customHeight="1">
       <c r="C403" s="2" t="s">
-        <v>735</v>
+        <v>751</v>
       </c>
     </row>
     <row r="404" ht="15.75" customHeight="1">
       <c r="C404" s="2" t="s">
-        <v>736</v>
+        <v>752</v>
       </c>
     </row>
     <row r="405" ht="15.75" customHeight="1">
       <c r="C405" s="2" t="s">
-        <v>737</v>
+        <v>753</v>
       </c>
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c r="C406" s="2" t="s">
-        <v>738</v>
+        <v>754</v>
       </c>
     </row>
     <row r="407" ht="15.75" customHeight="1">
       <c r="C407" s="2" t="s">
-        <v>739</v>
+        <v>755</v>
       </c>
     </row>
     <row r="408" ht="15.75" customHeight="1">
       <c r="C408" s="2" t="s">
-        <v>740</v>
+        <v>756</v>
       </c>
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c r="C409" s="2" t="s">
-        <v>741</v>
+        <v>757</v>
       </c>
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="C410" s="2" t="s">
-        <v>742</v>
+        <v>758</v>
       </c>
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c r="C411" s="2" t="s">
-        <v>743</v>
+        <v>759</v>
       </c>
     </row>
     <row r="412" ht="15.75" customHeight="1">
       <c r="C412" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="413" ht="15.75" customHeight="1">
       <c r="C413" s="2" t="s">
-        <v>744</v>
+        <v>760</v>
       </c>
     </row>
     <row r="414" ht="15.75" customHeight="1">
       <c r="C414" s="2" t="s">
-        <v>745</v>
+        <v>761</v>
       </c>
     </row>
     <row r="415" ht="15.75" customHeight="1">
       <c r="C415" s="2" t="s">
-        <v>746</v>
+        <v>762</v>
       </c>
     </row>
     <row r="416" ht="15.75" customHeight="1">
       <c r="C416" s="2" t="s">
-        <v>747</v>
+        <v>763</v>
       </c>
     </row>
     <row r="417" ht="15.75" customHeight="1">
       <c r="C417" s="2" t="s">
-        <v>748</v>
+        <v>764</v>
       </c>
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c r="C418" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
     </row>
     <row r="419" ht="15.75" customHeight="1">
       <c r="C419" s="2" t="s">
-        <v>750</v>
+        <v>766</v>
       </c>
     </row>
     <row r="420" ht="15.75" customHeight="1">
       <c r="C420" s="2" t="s">
-        <v>751</v>
+        <v>767</v>
       </c>
     </row>
     <row r="421" ht="15.75" customHeight="1">
       <c r="C421" s="2" t="s">
-        <v>752</v>
+        <v>768</v>
       </c>
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c r="C422" s="2" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c r="C423" s="2" t="s">
-        <v>754</v>
+        <v>770</v>
       </c>
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c r="C424" s="2" t="s">
-        <v>755</v>
+        <v>771</v>
       </c>
     </row>
     <row r="425" ht="15.75" customHeight="1">
       <c r="C425" s="2" t="s">
-        <v>756</v>
+        <v>772</v>
       </c>
     </row>
     <row r="426" ht="15.75" customHeight="1">
       <c r="C426" s="2" t="s">
-        <v>757</v>
+        <v>773</v>
       </c>
     </row>
     <row r="427" ht="15.75" customHeight="1">
       <c r="C427" s="2" t="s">
-        <v>758</v>
+        <v>774</v>
       </c>
     </row>
     <row r="428" ht="15.75" customHeight="1">
       <c r="C428" s="2" t="s">
-        <v>759</v>
+        <v>775</v>
       </c>
     </row>
     <row r="429" ht="15.75" customHeight="1">
       <c r="C429" s="2" t="s">
-        <v>760</v>
+        <v>776</v>
       </c>
     </row>
     <row r="430" ht="15.75" customHeight="1">
       <c r="C430" s="2" t="s">
-        <v>761</v>
+        <v>777</v>
       </c>
     </row>
     <row r="431" ht="15.75" customHeight="1">
       <c r="C431" s="2" t="s">
-        <v>762</v>
+        <v>778</v>
       </c>
     </row>
     <row r="432" ht="15.75" customHeight="1">
       <c r="C432" s="2" t="s">
-        <v>763</v>
+        <v>779</v>
       </c>
     </row>
     <row r="433" ht="15.75" customHeight="1">
       <c r="C433" s="2" t="s">
-        <v>764</v>
+        <v>780</v>
       </c>
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c r="C434" s="2" t="s">
-        <v>765</v>
+        <v>781</v>
       </c>
     </row>
     <row r="435" ht="15.75" customHeight="1">
       <c r="C435" s="2" t="s">
-        <v>766</v>
+        <v>782</v>
       </c>
     </row>
     <row r="436" ht="15.75" customHeight="1">
       <c r="C436" s="2" t="s">
-        <v>767</v>
+        <v>783</v>
       </c>
     </row>
     <row r="437" ht="15.75" customHeight="1">
       <c r="C437" s="2" t="s">
-        <v>768</v>
+        <v>784</v>
       </c>
     </row>
     <row r="438" ht="15.75" customHeight="1">
       <c r="C438" s="2" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
     </row>
     <row r="439" ht="15.75" customHeight="1">
       <c r="C439" s="2" t="s">
-        <v>770</v>
+        <v>786</v>
       </c>
     </row>
     <row r="440" ht="15.75" customHeight="1">
       <c r="C440" s="2" t="s">
-        <v>771</v>
+        <v>787</v>
       </c>
     </row>
     <row r="441" ht="15.75" customHeight="1">
       <c r="C441" s="2" t="s">
-        <v>772</v>
+        <v>788</v>
       </c>
     </row>
     <row r="442" ht="15.75" customHeight="1">
       <c r="C442" s="2" t="s">
-        <v>773</v>
+        <v>789</v>
       </c>
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c r="C443" s="2" t="s">
-        <v>774</v>
+        <v>790</v>
       </c>
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c r="C444" s="2" t="s">
-        <v>775</v>
+        <v>791</v>
       </c>
     </row>
     <row r="445" ht="15.75" customHeight="1">
       <c r="C445" s="2" t="s">
-        <v>776</v>
+        <v>792</v>
       </c>
     </row>
     <row r="446" ht="15.75" customHeight="1">
       <c r="C446" s="2" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
     </row>
     <row r="447" ht="15.75" customHeight="1">
       <c r="C447" s="2" t="s">
-        <v>778</v>
+        <v>794</v>
       </c>
     </row>
     <row r="448" ht="15.75" customHeight="1">
       <c r="C448" s="2" t="s">
-        <v>779</v>
+        <v>795</v>
       </c>
     </row>
     <row r="449" ht="15.75" customHeight="1">
       <c r="C449" s="2" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
     </row>
     <row r="450" ht="15.75" customHeight="1">
       <c r="C450" s="2" t="s">
-        <v>781</v>
+        <v>797</v>
       </c>
     </row>
     <row r="451" ht="15.75" customHeight="1">
       <c r="C451" s="2" t="s">
-        <v>782</v>
+        <v>798</v>
       </c>
     </row>
     <row r="452" ht="15.75" customHeight="1">
       <c r="C452" s="2" t="s">
-        <v>783</v>
+        <v>799</v>
       </c>
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c r="C453" s="2" t="s">
-        <v>784</v>
+        <v>800</v>
       </c>
     </row>
     <row r="454" ht="15.75" customHeight="1">
       <c r="C454" s="2" t="s">
-        <v>785</v>
+        <v>801</v>
       </c>
     </row>
     <row r="455" ht="15.75" customHeight="1">
       <c r="C455" s="2" t="s">
-        <v>786</v>
+        <v>802</v>
       </c>
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c r="C456" s="2" t="s">
-        <v>787</v>
+        <v>803</v>
       </c>
     </row>
     <row r="457" ht="15.75" customHeight="1">
       <c r="C457" s="2" t="s">
-        <v>788</v>
+        <v>804</v>
       </c>
     </row>
     <row r="458" ht="15.75" customHeight="1">
       <c r="C458" s="2" t="s">
-        <v>789</v>
+        <v>805</v>
       </c>
     </row>
     <row r="459" ht="15.75" customHeight="1">
       <c r="C459" s="2" t="s">
-        <v>790</v>
+        <v>806</v>
       </c>
     </row>
     <row r="460" ht="15.75" customHeight="1">
       <c r="C460" s="2" t="s">
-        <v>791</v>
+        <v>807</v>
       </c>
     </row>
     <row r="461" ht="15.75" customHeight="1">
       <c r="C461" s="2" t="s">
-        <v>792</v>
+        <v>808</v>
       </c>
     </row>
     <row r="462" ht="15.75" customHeight="1">
       <c r="C462" s="2" t="s">
-        <v>793</v>
+        <v>809</v>
       </c>
     </row>
     <row r="463" ht="15.75" customHeight="1">
       <c r="C463" s="2" t="s">
-        <v>794</v>
+        <v>810</v>
       </c>
     </row>
     <row r="464" ht="15.75" customHeight="1">
       <c r="C464" s="2" t="s">
-        <v>795</v>
+        <v>811</v>
       </c>
     </row>
     <row r="465" ht="15.75" customHeight="1">
       <c r="C465" s="2" t="s">
-        <v>796</v>
+        <v>812</v>
       </c>
     </row>
     <row r="466" ht="15.75" customHeight="1">
       <c r="C466" s="2" t="s">
-        <v>797</v>
+        <v>813</v>
       </c>
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c r="C467" s="2" t="s">
-        <v>798</v>
+        <v>814</v>
       </c>
     </row>
     <row r="468" ht="15.75" customHeight="1">
       <c r="C468" s="2" t="s">
-        <v>799</v>
+        <v>815</v>
       </c>
     </row>
     <row r="469" ht="15.75" customHeight="1">
       <c r="C469" s="2" t="s">
-        <v>800</v>
+        <v>816</v>
       </c>
     </row>
     <row r="470" ht="15.75" customHeight="1">
       <c r="C470" s="2" t="s">
-        <v>801</v>
+        <v>817</v>
       </c>
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c r="C471" s="2" t="s">
-        <v>802</v>
+        <v>818</v>
       </c>
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="C472" s="2" t="s">
-        <v>803</v>
+        <v>819</v>
       </c>
     </row>
     <row r="473" ht="15.75" customHeight="1">
       <c r="C473" s="2" t="s">
-        <v>804</v>
+        <v>820</v>
       </c>
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c r="C474" s="2" t="s">
-        <v>805</v>
+        <v>821</v>
       </c>
     </row>
     <row r="475" ht="15.75" customHeight="1">
       <c r="C475" s="2" t="s">
-        <v>806</v>
+        <v>822</v>
       </c>
     </row>
     <row r="476" ht="15.75" customHeight="1">
       <c r="C476" s="2" t="s">
-        <v>807</v>
+        <v>823</v>
       </c>
     </row>
     <row r="477" ht="15.75" customHeight="1">
       <c r="C477" s="2" t="s">
-        <v>808</v>
+        <v>824</v>
       </c>
     </row>
     <row r="478" ht="15.75" customHeight="1">
       <c r="C478" s="2" t="s">
-        <v>809</v>
+        <v>825</v>
       </c>
     </row>
     <row r="479" ht="15.75" customHeight="1">
       <c r="C479" s="2" t="s">
-        <v>810</v>
+        <v>826</v>
       </c>
     </row>
     <row r="480" ht="15.75" customHeight="1">
       <c r="C480" s="2" t="s">
-        <v>811</v>
+        <v>827</v>
       </c>
     </row>
     <row r="481" ht="15.75" customHeight="1">
       <c r="C481" s="2" t="s">
-        <v>812</v>
+        <v>828</v>
       </c>
     </row>
     <row r="482" ht="15.75" customHeight="1">
       <c r="C482" s="2" t="s">
-        <v>813</v>
+        <v>829</v>
       </c>
     </row>
     <row r="483" ht="15.75" customHeight="1">
       <c r="C483" s="2" t="s">
-        <v>814</v>
+        <v>830</v>
       </c>
     </row>
     <row r="484" ht="15.75" customHeight="1">
       <c r="C484" s="2" t="s">
-        <v>815</v>
+        <v>831</v>
       </c>
     </row>
     <row r="485" ht="15.75" customHeight="1">
       <c r="C485" s="2" t="s">
-        <v>816</v>
+        <v>832</v>
       </c>
     </row>
     <row r="486" ht="15.75" customHeight="1">
       <c r="C486" s="2" t="s">
-        <v>817</v>
+        <v>833</v>
       </c>
     </row>
     <row r="487" ht="15.75" customHeight="1">
       <c r="C487" s="2" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
     </row>
     <row r="488" ht="15.75" customHeight="1">
       <c r="C488" s="2" t="s">
-        <v>819</v>
+        <v>835</v>
       </c>
     </row>
     <row r="489" ht="15.75" customHeight="1">
       <c r="C489" s="2" t="s">
-        <v>820</v>
+        <v>836</v>
       </c>
     </row>
     <row r="490" ht="15.75" customHeight="1">
       <c r="C490" s="2" t="s">
-        <v>821</v>
+        <v>837</v>
       </c>
     </row>
     <row r="491" ht="15.75" customHeight="1">
       <c r="C491" s="2" t="s">
-        <v>822</v>
+        <v>838</v>
       </c>
     </row>
     <row r="492" ht="15.75" customHeight="1">
       <c r="C492" s="2" t="s">
-        <v>823</v>
+        <v>839</v>
       </c>
     </row>
     <row r="493" ht="15.75" customHeight="1"/>

--- a/data/uploads/ahd_screening.xlsx
+++ b/data/uploads/ahd_screening.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="844">
   <si>
     <t>name</t>
   </si>
@@ -308,6 +308,9 @@
     <t>r1iipkObaWo</t>
   </si>
   <si>
+    <t>who_clinical_stage_total_screened</t>
+  </si>
+  <si>
     <t>Most Recent VL</t>
   </si>
   <si>
@@ -626,7 +629,7 @@
     <t>concept_name | obs_value_coded</t>
   </si>
   <si>
-    <t>Patient pregnant | Yes</t>
+    <t>*pregnant | Yes</t>
   </si>
   <si>
     <t>sex_breastfeeding</t>
@@ -638,7 +641,7 @@
     <t>sex_female_non-pregnant</t>
   </si>
   <si>
-    <t>Patient pregnant | No</t>
+    <t>*pregnant | No</t>
   </si>
   <si>
     <t>Is patient breast feeding? | No</t>
@@ -806,21 +809,33 @@
     <t>who_clinical_stage_who_1</t>
   </si>
   <si>
+    <t>WHO stage</t>
+  </si>
+  <si>
+    <t>*WHO stage I</t>
+  </si>
+  <si>
     <t>who_clinical_stage_who_2</t>
   </si>
   <si>
+    <t>*WHO stage II</t>
+  </si>
+  <si>
     <t>who_clinical_stage_who_3</t>
   </si>
   <si>
+    <t>*WHO stage III</t>
+  </si>
+  <si>
     <t>who_clinical_stage_who_4</t>
   </si>
   <si>
+    <t>*WHO stage IV</t>
+  </si>
+  <si>
     <t>who_clinical_stage_unknown_missing</t>
   </si>
   <si>
-    <t>who_clinical_stage_total_screened</t>
-  </si>
-  <si>
     <t>most_recent_vl_not_done</t>
   </si>
   <si>
@@ -2505,9 +2520,6 @@
   </si>
   <si>
     <t>Who is present as guardian?</t>
-  </si>
-  <si>
-    <t>WHO stage</t>
   </si>
   <si>
     <t>Who stages criteria present</t>
@@ -3819,7 +3831,9 @@
         <v>23</v>
       </c>
       <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
+      <c r="C49" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
       <c r="G49" s="10"/>
@@ -3831,7 +3845,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>13</v>
@@ -3850,11 +3864,11 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
@@ -3867,11 +3881,11 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
@@ -3884,11 +3898,11 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
@@ -3905,7 +3919,7 @@
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -3933,7 +3947,7 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>13</v>
@@ -3952,11 +3966,11 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E57" s="10"/>
       <c r="F57" s="10"/>
@@ -3969,11 +3983,11 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E58" s="10"/>
       <c r="F58" s="10"/>
@@ -3986,11 +4000,11 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E59" s="10"/>
       <c r="F59" s="10"/>
@@ -4007,7 +4021,7 @@
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E60" s="10"/>
       <c r="F60" s="10"/>
@@ -4035,7 +4049,7 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>13</v>
@@ -4054,11 +4068,11 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E63" s="10"/>
       <c r="F63" s="10"/>
@@ -4071,11 +4085,11 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E64" s="10"/>
       <c r="F64" s="10"/>
@@ -4088,11 +4102,11 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E65" s="10"/>
       <c r="F65" s="10"/>
@@ -4120,7 +4134,7 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>13</v>
@@ -4139,11 +4153,11 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E68" s="10"/>
       <c r="F68" s="10"/>
@@ -4156,11 +4170,11 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E69" s="10"/>
       <c r="F69" s="10"/>
@@ -4173,11 +4187,11 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E70" s="10"/>
       <c r="F70" s="10"/>
@@ -4205,7 +4219,7 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>13</v>
@@ -4224,11 +4238,11 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
@@ -4241,11 +4255,11 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E74" s="10"/>
       <c r="F74" s="10"/>
@@ -4258,11 +4272,11 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E75" s="10"/>
       <c r="F75" s="10"/>
@@ -4290,7 +4304,7 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>13</v>
@@ -4309,11 +4323,11 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
@@ -4326,11 +4340,11 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
@@ -4343,11 +4357,11 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
@@ -4375,7 +4389,7 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>13</v>
@@ -4394,11 +4408,11 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
@@ -4411,11 +4425,11 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
@@ -4428,11 +4442,11 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
@@ -4460,7 +4474,7 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>13</v>
@@ -4479,11 +4493,11 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
@@ -4496,11 +4510,11 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
@@ -4513,11 +4527,11 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
@@ -4545,7 +4559,7 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>13</v>
@@ -4568,7 +4582,7 @@
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
@@ -4585,7 +4599,7 @@
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
@@ -4602,7 +4616,7 @@
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
@@ -4630,7 +4644,7 @@
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>13</v>
@@ -4649,11 +4663,11 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
@@ -4666,11 +4680,11 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
@@ -4683,11 +4697,11 @@
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
@@ -4700,11 +4714,11 @@
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
@@ -4717,11 +4731,11 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -4734,11 +4748,11 @@
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
@@ -4751,7 +4765,7 @@
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="20"/>
@@ -4766,7 +4780,7 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>13</v>
@@ -4785,11 +4799,11 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -4802,11 +4816,11 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -4819,11 +4833,11 @@
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
@@ -4836,11 +4850,11 @@
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
@@ -4857,7 +4871,7 @@
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
@@ -4870,7 +4884,7 @@
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="20"/>
@@ -17343,76 +17357,76 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
@@ -17420,22 +17434,22 @@
         <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -17462,31 +17476,31 @@
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -17508,31 +17522,31 @@
         <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -17554,37 +17568,37 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -17604,19 +17618,19 @@
         <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
@@ -17642,25 +17656,25 @@
         <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>208</v>
-      </c>
       <c r="D7" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G7" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -17684,31 +17698,31 @@
         <v>29</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G8" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>25</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -17730,25 +17744,25 @@
         <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G9" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -17775,16 +17789,16 @@
         <v>32</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
@@ -17810,31 +17824,31 @@
         <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -17856,31 +17870,31 @@
         <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="J12" s="18" t="s">
         <v>221</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>220</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -17902,31 +17916,31 @@
         <v>39</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -17951,22 +17965,22 @@
         <v>40</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I14" s="18"/>
       <c r="J14" s="18"/>
@@ -17990,19 +18004,19 @@
         <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -18028,19 +18042,19 @@
         <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -18066,19 +18080,19 @@
         <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -18104,19 +18118,19 @@
         <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -18145,16 +18159,16 @@
         <v>50</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -18180,31 +18194,31 @@
         <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F20" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="H20" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -18226,31 +18240,31 @@
         <v>55</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F21" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="H21" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -18272,31 +18286,31 @@
         <v>56</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F22" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="H22" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -18321,16 +18335,16 @@
         <v>57</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
@@ -18356,31 +18370,31 @@
         <v>60</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F24" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G24" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G24" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H24" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -18402,31 +18416,31 @@
         <v>62</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F25" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G25" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G25" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H25" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J25" s="18" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -18448,31 +18462,31 @@
         <v>64</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F26" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G26" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G26" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H26" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -18494,31 +18508,31 @@
         <v>66</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F27" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G27" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H27" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -18540,31 +18554,31 @@
         <v>68</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F28" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G28" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G28" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H28" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -18586,31 +18600,31 @@
         <v>70</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F29" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G29" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G29" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H29" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -18632,31 +18646,31 @@
         <v>72</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F30" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G30" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G30" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H30" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -18678,31 +18692,31 @@
         <v>74</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F31" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G31" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G31" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H31" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -18724,31 +18738,31 @@
         <v>76</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F32" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G32" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G32" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H32" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -18770,31 +18784,31 @@
         <v>78</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F33" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G33" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G33" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H33" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -18816,31 +18830,31 @@
         <v>80</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F34" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G34" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G34" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H34" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -18862,31 +18876,31 @@
         <v>82</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F35" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G35" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G35" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H35" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I35" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J35" s="18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -18911,22 +18925,22 @@
         <v>84</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F36" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G36" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="G36" s="24" t="s">
-        <v>194</v>
-      </c>
       <c r="H36" s="23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I36" s="18"/>
       <c r="J36" s="1"/>
@@ -18950,23 +18964,32 @@
         <v>87</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
+        <v>195</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G37" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="H37" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="I37" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>263</v>
+      </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -18987,24 +19010,32 @@
         <v>89</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
+        <v>195</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G38" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="H38" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="I38" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>265</v>
+      </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -19025,24 +19056,32 @@
         <v>91</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G39" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="H39" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="C39" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
+      <c r="I39" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="J39" s="18" t="s">
+        <v>267</v>
+      </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -19063,24 +19102,32 @@
         <v>93</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
+        <v>195</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G40" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="H40" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>269</v>
+      </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -19101,24 +19148,32 @@
         <v>94</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
+        <v>195</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G41" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="H41" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="I41" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="J41" s="18" t="s">
+        <v>236</v>
+      </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -19135,26 +19190,32 @@
       <c r="X41" s="1"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="2"/>
+      <c r="A42" s="15" t="s">
+        <v>95</v>
+      </c>
       <c r="B42" s="2" t="s">
-        <v>265</v>
+        <v>95</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
+        <v>195</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G42" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="H42" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -19172,22 +19233,22 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -19210,22 +19271,22 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -19248,22 +19309,22 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -19286,22 +19347,22 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -19325,19 +19386,19 @@
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -19360,22 +19421,22 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -19398,22 +19459,22 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -19436,22 +19497,22 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -19474,22 +19535,22 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -19513,19 +19574,19 @@
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -19548,22 +19609,22 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -19586,22 +19647,22 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -19624,22 +19685,22 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -19663,19 +19724,19 @@
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -19698,22 +19759,22 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -19736,22 +19797,22 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -19774,22 +19835,22 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -19813,19 +19874,19 @@
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -19848,22 +19909,22 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -19886,22 +19947,22 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -19924,22 +19985,22 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -19963,19 +20024,19 @@
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -19998,22 +20059,22 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -20036,22 +20097,22 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -20074,22 +20135,22 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -20113,19 +20174,19 @@
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D68" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -20148,20 +20209,20 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -20184,20 +20245,20 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -20220,20 +20281,20 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -20258,16 +20319,16 @@
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D72" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -20290,22 +20351,22 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -20328,22 +20389,22 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D74" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -20366,22 +20427,22 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
@@ -20405,19 +20466,19 @@
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="2"/>
       <c r="B76" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D76" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
@@ -20440,20 +20501,20 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
@@ -20476,20 +20537,20 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D78" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -20512,20 +20573,20 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -20550,16 +20611,16 @@
       <c r="A80" s="20"/>
       <c r="B80" s="1"/>
       <c r="C80" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D80" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -20582,20 +20643,20 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -20618,20 +20679,20 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D82" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
@@ -20654,20 +20715,20 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
@@ -20692,16 +20753,16 @@
       <c r="A84" s="20"/>
       <c r="B84" s="1"/>
       <c r="C84" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D84" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
@@ -20724,20 +20785,20 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D85" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
@@ -20760,20 +20821,20 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D86" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
@@ -20796,20 +20857,20 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D87" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
@@ -20832,20 +20893,20 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D88" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
@@ -20868,20 +20929,20 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D89" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
@@ -20904,20 +20965,20 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D90" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
@@ -20942,16 +21003,16 @@
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D91" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
@@ -20974,20 +21035,20 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D92" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
@@ -21010,20 +21071,20 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D93" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
@@ -21046,20 +21107,20 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D94" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
@@ -21082,20 +21143,20 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D95" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
@@ -21118,20 +21179,20 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D96" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
@@ -21156,16 +21217,16 @@
       <c r="A97" s="20"/>
       <c r="B97" s="1"/>
       <c r="C97" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D97" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
@@ -44450,24 +44511,24 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1"/>
@@ -45488,15 +45549,15 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1"/>
@@ -46520,10 +46581,10 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -46538,13 +46599,13 @@
         <v>ahd_screening</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -52562,883 +52623,883 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="I1" s="25" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="B9" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="B10" s="2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="B11" s="2" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="B12" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="B13" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="B14" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="B15" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="B16" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="B17" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="B18" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="B19" s="2" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="B20" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="B25" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="B26" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="C32" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="C33" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="C34" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="C35" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="C36" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="C37" s="2" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="C38" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="C39" s="2" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="C40" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="C41" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="C42" s="2" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="C43" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="C44" s="2" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="C45" s="2" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="C46" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="C47" s="2" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="C48" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="C49" s="2" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="C50" s="2" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="C51" s="2" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="C52" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="C53" s="2" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="C54" s="2" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="C55" s="2" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="C56" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="C57" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="C58" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="C59" s="2" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="C60" s="2" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="C61" s="2" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="C62" s="2" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="C63" s="2" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="C64" s="2" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="C65" s="2" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="C66" s="2" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="C67" s="2" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="C68" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="C69" s="2" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="C70" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="C71" s="2" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="C72" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="C73" s="2" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="C74" s="2" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="C75" s="2" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="C76" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="C77" s="2" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="C78" s="2" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="C79" s="2" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="C80" s="2" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="C81" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="C82" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="C83" s="2" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="C84" s="2" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="C85" s="2" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="C86" s="2" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="C87" s="2" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="C88" s="2" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="C89" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="C90" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="C91" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="C92" s="2" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="C93" s="2" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="C94" s="2" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="C95" s="2" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="C96" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="C97" s="2" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="C98" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="C99" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="C100" s="2" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="C101" s="2" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="C102" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="C103" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="C104" s="2" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="C105" s="2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="C106" s="2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="C107" s="2" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="C108" s="2" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="C109" s="2" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="C110" s="2" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="C111" s="2" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="C112" s="2" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="C113" s="2" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="C114" s="2" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="C115" s="2" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="C116" s="2" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="C117" s="2" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="C118" s="2" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="C119" s="2" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="C120" s="2" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="C121" s="2" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="C122" s="2" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="C123" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="C124" s="2" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="C125" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="C126" s="2" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="C127" s="2" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="C128" s="2" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="C129" s="2" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="C130" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="C131" s="2" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="C132" s="2" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="C133" s="2" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="C134" s="2" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="C135" s="2" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="C136" s="2" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
@@ -53448,122 +53509,122 @@
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="C138" s="2" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="C139" s="2" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="C140" s="2" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="C141" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="C142" s="2" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="C143" s="2" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="C144" s="2" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="C145" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="C146" s="2" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="C147" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="C148" s="2" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="C149" s="2" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="C150" s="2" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="C151" s="2" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="C152" s="2" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="C153" s="2" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="C154" s="2" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="C155" s="2" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="C156" s="2" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="C157" s="2" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="C158" s="2" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="C159" s="2" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="C160" s="2" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="C161" s="2" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
@@ -53573,952 +53634,952 @@
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="C163" s="2" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="C164" s="2" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="C165" s="2" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="C166" s="2" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="C167" s="2" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="C168" s="2" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="C169" s="2" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="C170" s="2" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="C171" s="2" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="C172" s="2" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="C173" s="2" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="C174" s="2" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="C175" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="C176" s="2" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="C177" s="2" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="C178" s="2" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="C179" s="2" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="C180" s="2" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="C181" s="2" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="C182" s="2" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="C183" s="2" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="C184" s="2" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="C185" s="2" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="C186" s="2" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="C187" s="2" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="C188" s="2" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="C189" s="2" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="C190" s="2" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="C191" s="2" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="C192" s="2" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="C193" s="2" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="C194" s="2" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="C195" s="2" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="C196" s="2" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="C197" s="2" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="C198" s="2" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="C199" s="2" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="C200" s="2" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="C201" s="2" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="C202" s="2" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="C203" s="2" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="C204" s="2" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="C205" s="2" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="C206" s="2" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="C207" s="2" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="C208" s="2" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="C209" s="2" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="C210" s="2" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="C211" s="2" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="C212" s="2" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="C213" s="2" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="C214" s="2" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="C215" s="2" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="C216" s="2" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="C217" s="2" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="C218" s="2" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="C219" s="2" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="C220" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="C221" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="C222" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="C223" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="C224" s="2" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="C225" s="2" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="C226" s="2" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="C227" s="2" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="C228" s="2" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="C229" s="2" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="C230" s="2" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="C231" s="2" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="C232" s="2" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="C233" s="2" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="C234" s="2" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="C235" s="2" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="C236" s="2" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="C237" s="2" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="C238" s="2" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="C239" s="2" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="C240" s="2" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="C241" s="2" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="C242" s="2" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="243" ht="15.75" customHeight="1">
       <c r="C243" s="2" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
     </row>
     <row r="244" ht="15.75" customHeight="1">
       <c r="C244" s="2" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="C245" s="2" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="C246" s="2" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="C247" s="2" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="C248" s="2" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="249" ht="15.75" customHeight="1">
       <c r="C249" s="2" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="C250" s="2" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="C251" s="2" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
     <row r="252" ht="15.75" customHeight="1">
       <c r="C252" s="2" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="C253" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="C254" s="2" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="C255" s="2" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="C256" s="2" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="C257" s="2" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="C258" s="2" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="C259" s="2" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="C260" s="2" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="C261" s="2" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="C262" s="2" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="C263" s="2" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="C264" s="2" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="C265" s="2" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="C266" s="2" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="C267" s="2" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="C268" s="2" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="C269" s="2" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="C270" s="2" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="C271" s="2" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="C272" s="2" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="C273" s="2" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="C274" s="2" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="C275" s="2" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="C276" s="2" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="C277" s="2" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="C278" s="2" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="C279" s="2" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="C280" s="2" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="C281" s="2" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
     </row>
     <row r="282" ht="15.75" customHeight="1">
       <c r="C282" s="2" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="C283" s="2" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="C284" s="2" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="285" ht="15.75" customHeight="1">
       <c r="C285" s="2" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="C286" s="2" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="287" ht="15.75" customHeight="1">
       <c r="C287" s="2" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
     </row>
     <row r="288" ht="15.75" customHeight="1">
       <c r="C288" s="2" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="C289" s="2" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="C290" s="2" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="C291" s="2" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="C292" s="2" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="C293" s="2" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="C294" s="2" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="C295" s="2" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="C296" s="2" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="C297" s="2" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="C298" s="2" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="C299" s="2" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="C300" s="2" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="C301" s="2" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="C302" s="2" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="C303" s="2" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="C304" s="2" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="C305" s="2" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="C306" s="2" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="C307" s="2" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="C308" s="2" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="C309" s="2" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="C310" s="2" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="C311" s="2" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="C312" s="2" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="C313" s="2" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="C314" s="2" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="C315" s="2" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="C316" s="2" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="C317" s="2" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="C318" s="2" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="C319" s="2" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="C320" s="2" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="C321" s="2" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="C322" s="2" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="C323" s="2" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="C324" s="2" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="C325" s="2" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="C326" s="2" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="C327" s="2" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="C328" s="2" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="C329" s="2" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
     </row>
     <row r="330" ht="15.75" customHeight="1">
       <c r="C330" s="2" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="C331" s="2" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="C332" s="2" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="C333" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="C334" s="2" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="C335" s="2" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="C336" s="2" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="C337" s="2" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="C338" s="2" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="C339" s="2" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="C340" s="2" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="C341" s="2" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="C342" s="2" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="C343" s="2" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="C344" s="2" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="C345" s="2" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="C346" s="2" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
     </row>
     <row r="347" ht="15.75" customHeight="1">
       <c r="C347" s="2" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
     </row>
     <row r="348" ht="15.75" customHeight="1">
       <c r="C348" s="2" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
     </row>
     <row r="349" ht="15.75" customHeight="1">
       <c r="C349" s="2" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
     </row>
     <row r="350" ht="15.75" customHeight="1">
       <c r="C350" s="2" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
     </row>
     <row r="351" ht="15.75" customHeight="1">
       <c r="C351" s="2" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
     </row>
     <row r="352" ht="15.75" customHeight="1">
       <c r="C352" s="2" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
     </row>
     <row r="353" ht="15.75" customHeight="1">
@@ -54528,292 +54589,292 @@
     </row>
     <row r="354" ht="15.75" customHeight="1">
       <c r="C354" s="2" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
     </row>
     <row r="355" ht="15.75" customHeight="1">
       <c r="C355" s="2" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
     </row>
     <row r="356" ht="15.75" customHeight="1">
       <c r="C356" s="2" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="357" ht="15.75" customHeight="1">
       <c r="C357" s="2" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="358" ht="15.75" customHeight="1">
       <c r="C358" s="2" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
     </row>
     <row r="359" ht="15.75" customHeight="1">
       <c r="C359" s="2" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
     </row>
     <row r="360" ht="15.75" customHeight="1">
       <c r="C360" s="2" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
     </row>
     <row r="361" ht="15.75" customHeight="1">
       <c r="C361" s="2" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
     </row>
     <row r="362" ht="15.75" customHeight="1">
       <c r="C362" s="2" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
     </row>
     <row r="363" ht="15.75" customHeight="1">
       <c r="C363" s="2" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
     </row>
     <row r="364" ht="15.75" customHeight="1">
       <c r="C364" s="2" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
     </row>
     <row r="365" ht="15.75" customHeight="1">
       <c r="C365" s="2" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
     </row>
     <row r="366" ht="15.75" customHeight="1">
       <c r="C366" s="2" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
     </row>
     <row r="367" ht="15.75" customHeight="1">
       <c r="C367" s="2" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
     </row>
     <row r="368" ht="15.75" customHeight="1">
       <c r="C368" s="2" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
     </row>
     <row r="369" ht="15.75" customHeight="1">
       <c r="C369" s="2" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
     </row>
     <row r="370" ht="15.75" customHeight="1">
       <c r="C370" s="2" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
     </row>
     <row r="371" ht="15.75" customHeight="1">
       <c r="C371" s="2" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1">
       <c r="C372" s="2" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
     </row>
     <row r="373" ht="15.75" customHeight="1">
       <c r="C373" s="2" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
     </row>
     <row r="374" ht="15.75" customHeight="1">
       <c r="C374" s="2" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="375" ht="15.75" customHeight="1">
       <c r="C375" s="2" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="376" ht="15.75" customHeight="1">
       <c r="C376" s="2" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
     </row>
     <row r="377" ht="15.75" customHeight="1">
       <c r="C377" s="2" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
     </row>
     <row r="378" ht="15.75" customHeight="1">
       <c r="C378" s="2" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
     </row>
     <row r="379" ht="15.75" customHeight="1">
       <c r="C379" s="2" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
     </row>
     <row r="380" ht="15.75" customHeight="1">
       <c r="C380" s="2" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
     </row>
     <row r="381" ht="15.75" customHeight="1">
       <c r="C381" s="2" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
     </row>
     <row r="382" ht="15.75" customHeight="1">
       <c r="C382" s="2" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="383" ht="15.75" customHeight="1">
       <c r="C383" s="2" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
     </row>
     <row r="384" ht="15.75" customHeight="1">
       <c r="C384" s="2" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
     </row>
     <row r="385" ht="15.75" customHeight="1">
       <c r="C385" s="2" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
     </row>
     <row r="386" ht="15.75" customHeight="1">
       <c r="C386" s="2" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
     </row>
     <row r="387" ht="15.75" customHeight="1">
       <c r="C387" s="2" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
     </row>
     <row r="388" ht="15.75" customHeight="1">
       <c r="C388" s="2" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
     </row>
     <row r="389" ht="15.75" customHeight="1">
       <c r="C389" s="2" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
     </row>
     <row r="390" ht="15.75" customHeight="1">
       <c r="C390" s="2" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
     </row>
     <row r="391" ht="15.75" customHeight="1">
       <c r="C391" s="2" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
     </row>
     <row r="392" ht="15.75" customHeight="1">
       <c r="C392" s="2" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
     </row>
     <row r="393" ht="15.75" customHeight="1">
       <c r="C393" s="2" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
     </row>
     <row r="394" ht="15.75" customHeight="1">
       <c r="C394" s="2" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
     </row>
     <row r="395" ht="15.75" customHeight="1">
       <c r="C395" s="2" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
     </row>
     <row r="396" ht="15.75" customHeight="1">
       <c r="C396" s="2" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="C397" s="2" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
     </row>
     <row r="398" ht="15.75" customHeight="1">
       <c r="C398" s="2" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
     </row>
     <row r="399" ht="15.75" customHeight="1">
       <c r="C399" s="2" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
     </row>
     <row r="400" ht="15.75" customHeight="1">
       <c r="C400" s="2" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
     </row>
     <row r="401" ht="15.75" customHeight="1">
       <c r="C401" s="2" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
     </row>
     <row r="402" ht="15.75" customHeight="1">
       <c r="C402" s="2" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
     </row>
     <row r="403" ht="15.75" customHeight="1">
       <c r="C403" s="2" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
     </row>
     <row r="404" ht="15.75" customHeight="1">
       <c r="C404" s="2" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
     </row>
     <row r="405" ht="15.75" customHeight="1">
       <c r="C405" s="2" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c r="C406" s="2" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
     </row>
     <row r="407" ht="15.75" customHeight="1">
       <c r="C407" s="2" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
     </row>
     <row r="408" ht="15.75" customHeight="1">
       <c r="C408" s="2" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c r="C409" s="2" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="C410" s="2" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c r="C411" s="2" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
     </row>
     <row r="412" ht="15.75" customHeight="1">
@@ -54823,402 +54884,402 @@
     </row>
     <row r="413" ht="15.75" customHeight="1">
       <c r="C413" s="2" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
     </row>
     <row r="414" ht="15.75" customHeight="1">
       <c r="C414" s="2" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
     </row>
     <row r="415" ht="15.75" customHeight="1">
       <c r="C415" s="2" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
     </row>
     <row r="416" ht="15.75" customHeight="1">
       <c r="C416" s="2" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
     </row>
     <row r="417" ht="15.75" customHeight="1">
       <c r="C417" s="2" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c r="C418" s="2" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
     </row>
     <row r="419" ht="15.75" customHeight="1">
       <c r="C419" s="2" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
     </row>
     <row r="420" ht="15.75" customHeight="1">
       <c r="C420" s="2" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="421" ht="15.75" customHeight="1">
       <c r="C421" s="2" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c r="C422" s="2" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c r="C423" s="2" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c r="C424" s="2" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
     </row>
     <row r="425" ht="15.75" customHeight="1">
       <c r="C425" s="2" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
     </row>
     <row r="426" ht="15.75" customHeight="1">
       <c r="C426" s="2" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
     </row>
     <row r="427" ht="15.75" customHeight="1">
       <c r="C427" s="2" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
     </row>
     <row r="428" ht="15.75" customHeight="1">
       <c r="C428" s="2" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
     </row>
     <row r="429" ht="15.75" customHeight="1">
       <c r="C429" s="2" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
     </row>
     <row r="430" ht="15.75" customHeight="1">
       <c r="C430" s="2" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
     </row>
     <row r="431" ht="15.75" customHeight="1">
       <c r="C431" s="2" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
     </row>
     <row r="432" ht="15.75" customHeight="1">
       <c r="C432" s="2" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
     </row>
     <row r="433" ht="15.75" customHeight="1">
       <c r="C433" s="2" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c r="C434" s="2" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
     </row>
     <row r="435" ht="15.75" customHeight="1">
       <c r="C435" s="2" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
     </row>
     <row r="436" ht="15.75" customHeight="1">
       <c r="C436" s="2" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
     </row>
     <row r="437" ht="15.75" customHeight="1">
       <c r="C437" s="2" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
     </row>
     <row r="438" ht="15.75" customHeight="1">
       <c r="C438" s="2" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
     </row>
     <row r="439" ht="15.75" customHeight="1">
       <c r="C439" s="2" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
     </row>
     <row r="440" ht="15.75" customHeight="1">
       <c r="C440" s="2" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
     </row>
     <row r="441" ht="15.75" customHeight="1">
       <c r="C441" s="2" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
     </row>
     <row r="442" ht="15.75" customHeight="1">
       <c r="C442" s="2" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c r="C443" s="2" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c r="C444" s="2" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
     </row>
     <row r="445" ht="15.75" customHeight="1">
       <c r="C445" s="2" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
     </row>
     <row r="446" ht="15.75" customHeight="1">
       <c r="C446" s="2" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
     </row>
     <row r="447" ht="15.75" customHeight="1">
       <c r="C447" s="2" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
     </row>
     <row r="448" ht="15.75" customHeight="1">
       <c r="C448" s="2" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
     </row>
     <row r="449" ht="15.75" customHeight="1">
       <c r="C449" s="2" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
     </row>
     <row r="450" ht="15.75" customHeight="1">
       <c r="C450" s="2" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
     </row>
     <row r="451" ht="15.75" customHeight="1">
       <c r="C451" s="2" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
     </row>
     <row r="452" ht="15.75" customHeight="1">
       <c r="C452" s="2" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c r="C453" s="2" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
     </row>
     <row r="454" ht="15.75" customHeight="1">
       <c r="C454" s="2" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
     </row>
     <row r="455" ht="15.75" customHeight="1">
       <c r="C455" s="2" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c r="C456" s="2" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
     </row>
     <row r="457" ht="15.75" customHeight="1">
       <c r="C457" s="2" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
     </row>
     <row r="458" ht="15.75" customHeight="1">
       <c r="C458" s="2" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
     </row>
     <row r="459" ht="15.75" customHeight="1">
       <c r="C459" s="2" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
     </row>
     <row r="460" ht="15.75" customHeight="1">
       <c r="C460" s="2" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
     </row>
     <row r="461" ht="15.75" customHeight="1">
       <c r="C461" s="2" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
     </row>
     <row r="462" ht="15.75" customHeight="1">
       <c r="C462" s="2" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
     </row>
     <row r="463" ht="15.75" customHeight="1">
       <c r="C463" s="2" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
     </row>
     <row r="464" ht="15.75" customHeight="1">
       <c r="C464" s="2" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
     </row>
     <row r="465" ht="15.75" customHeight="1">
       <c r="C465" s="2" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
     </row>
     <row r="466" ht="15.75" customHeight="1">
       <c r="C466" s="2" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c r="C467" s="2" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
     </row>
     <row r="468" ht="15.75" customHeight="1">
       <c r="C468" s="2" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
     </row>
     <row r="469" ht="15.75" customHeight="1">
       <c r="C469" s="2" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
     </row>
     <row r="470" ht="15.75" customHeight="1">
       <c r="C470" s="2" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c r="C471" s="2" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="C472" s="2" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
     </row>
     <row r="473" ht="15.75" customHeight="1">
       <c r="C473" s="2" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c r="C474" s="2" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
     </row>
     <row r="475" ht="15.75" customHeight="1">
       <c r="C475" s="2" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
     </row>
     <row r="476" ht="15.75" customHeight="1">
       <c r="C476" s="2" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
     </row>
     <row r="477" ht="15.75" customHeight="1">
       <c r="C477" s="2" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
     </row>
     <row r="478" ht="15.75" customHeight="1">
       <c r="C478" s="2" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
     </row>
     <row r="479" ht="15.75" customHeight="1">
       <c r="C479" s="2" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
     </row>
     <row r="480" ht="15.75" customHeight="1">
       <c r="C480" s="2" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
     </row>
     <row r="481" ht="15.75" customHeight="1">
       <c r="C481" s="2" t="s">
-        <v>828</v>
+        <v>262</v>
       </c>
     </row>
     <row r="482" ht="15.75" customHeight="1">
       <c r="C482" s="2" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="483" ht="15.75" customHeight="1">
       <c r="C483" s="2" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
     </row>
     <row r="484" ht="15.75" customHeight="1">
       <c r="C484" s="2" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
     </row>
     <row r="485" ht="15.75" customHeight="1">
       <c r="C485" s="2" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
     </row>
     <row r="486" ht="15.75" customHeight="1">
       <c r="C486" s="2" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
     </row>
     <row r="487" ht="15.75" customHeight="1">
       <c r="C487" s="2" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
     </row>
     <row r="488" ht="15.75" customHeight="1">
       <c r="C488" s="2" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
     </row>
     <row r="489" ht="15.75" customHeight="1">
       <c r="C489" s="2" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
     </row>
     <row r="490" ht="15.75" customHeight="1">
       <c r="C490" s="2" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
     </row>
     <row r="491" ht="15.75" customHeight="1">
       <c r="C491" s="2" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
     </row>
     <row r="492" ht="15.75" customHeight="1">
       <c r="C492" s="2" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
     </row>
     <row r="493" ht="15.75" customHeight="1"/>
